--- a/Service_Watch_Test/DEET_ST_Synergy_SW_Parameters_Rev5.2 REQ 552-update.xlsx
+++ b/Service_Watch_Test/DEET_ST_Synergy_SW_Parameters_Rev5.2 REQ 552-update.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tranetechnologies-my.sharepoint.com/personal/quant_vo_tranetechnologies_com/Documents/Documents/SysEng/Work/Standardize Service Watch Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u245231\Quan_Vo\Local_Dev\complete-pandas-tutorial\Service_Watch_Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{F8C80F46-C73B-4FDF-BE47-C5F66621CC0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0D41194-9BAD-4EA6-A9FC-CCCA2A2BEF40}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE62AD8-C151-489A-9DDF-33040FA5C8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5364" yWindow="420" windowWidth="17280" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$1:$L$513</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3678,7 +3678,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3823,12 +3823,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3841,6 +3835,57 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3924,10 +3969,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4193,26 +4234,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L513"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="35"/>
-    <col min="2" max="2" width="18.140625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="35"/>
-    <col min="4" max="4" width="44.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.85546875" style="35" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" style="35" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="35" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" style="44" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="35" customWidth="1"/>
-    <col min="11" max="11" width="39.7109375" style="35" customWidth="1"/>
-    <col min="12" max="12" width="42.7109375" style="35" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="35"/>
+    <col min="1" max="1" width="9.109375" style="35"/>
+    <col min="2" max="2" width="18.109375" style="35" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="35"/>
+    <col min="4" max="4" width="44.5546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.88671875" style="35" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" style="35" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="35" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" style="44" customWidth="1"/>
+    <col min="10" max="10" width="20.5546875" style="35" customWidth="1"/>
+    <col min="11" max="11" width="39.6640625" style="35" customWidth="1"/>
+    <col min="12" max="12" width="42.6640625" style="35" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="34" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="34" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -4250,7 +4290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="45"/>
       <c r="B2" s="45" t="s">
         <v>12</v>
@@ -4284,7 +4324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>21</v>
@@ -4316,120 +4356,140 @@
       </c>
       <c r="L3" s="19"/>
     </row>
-    <row r="4" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
-      <c r="B4" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="36"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-    </row>
-    <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="I4" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="39"/>
+    </row>
+    <row r="5" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="B5" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="36"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="I5" s="37"/>
+      <c r="J5" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L5" s="39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
-      <c r="B6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="36"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="38">
+        <v>3</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="39"/>
+    </row>
+    <row r="8" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -4437,48 +4497,50 @@
       <c r="F8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="G8" s="6"/>
       <c r="H8" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I8" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>44</v>
+        <v>156</v>
+      </c>
+      <c r="J8" s="38">
+        <v>4</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="39"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6"/>
       <c r="H9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="36"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="J9" s="38">
+        <v>203</v>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="39"/>
+    </row>
+    <row r="10" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="15" t="s">
         <v>48</v>
@@ -4500,7 +4562,7 @@
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>21</v>
@@ -4530,7 +4592,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="21"/>
     </row>
-    <row r="12" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="15" t="s">
         <v>48</v>
@@ -4552,7 +4614,7 @@
       <c r="K12" s="12"/>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="15" t="s">
         <v>48</v>
@@ -4574,7 +4636,7 @@
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
     </row>
-    <row r="14" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="15" t="s">
         <v>48</v>
@@ -4596,37 +4658,37 @@
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" s="38">
+        <v>204</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="39"/>
+    </row>
+    <row r="16" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="15" t="s">
         <v>48</v>
@@ -4648,7 +4710,7 @@
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="15" t="s">
         <v>48</v>
@@ -4670,7 +4732,7 @@
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="15" t="s">
         <v>48</v>
@@ -4692,7 +4754,7 @@
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="15" t="s">
         <v>48</v>
@@ -4714,67 +4776,67 @@
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="37"/>
+        <v>23</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>165</v>
+      </c>
       <c r="J20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L20" s="39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="39"/>
+    </row>
+    <row r="21" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="6"/>
       <c r="H21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="36"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="L21" s="5"/>
-    </row>
-    <row r="22" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" s="38">
+        <v>5</v>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="39"/>
+    </row>
+    <row r="22" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="15" t="s">
         <v>48</v>
@@ -4796,7 +4858,7 @@
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>21</v>
@@ -4828,7 +4890,7 @@
       </c>
       <c r="L23" s="21"/>
     </row>
-    <row r="24" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="15" t="s">
         <v>48</v>
@@ -4850,7 +4912,7 @@
       <c r="K24" s="12"/>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="15" t="s">
         <v>48</v>
@@ -4872,7 +4934,7 @@
       <c r="K25" s="12"/>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="15" t="s">
         <v>48</v>
@@ -4894,37 +4956,37 @@
       <c r="K26" s="12"/>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>92</v>
+        <v>175</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>176</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>177</v>
+      </c>
       <c r="J27" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="39"/>
+    </row>
+    <row r="28" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="15" t="s">
         <v>48</v>
@@ -4946,7 +5008,7 @@
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="15" t="s">
         <v>48</v>
@@ -4968,7 +5030,7 @@
       <c r="K29" s="12"/>
       <c r="L29" s="12"/>
     </row>
-    <row r="30" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="15" t="s">
         <v>48</v>
@@ -4990,7 +5052,7 @@
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="15" t="s">
         <v>48</v>
@@ -5012,7 +5074,7 @@
       <c r="K31" s="12"/>
       <c r="L31" s="12"/>
     </row>
-    <row r="32" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="15" t="s">
         <v>48</v>
@@ -5034,7 +5096,7 @@
       <c r="K32" s="12"/>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="15" t="s">
         <v>48</v>
@@ -5056,7 +5118,7 @@
       <c r="K33" s="12"/>
       <c r="L33" s="12"/>
     </row>
-    <row r="34" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="15" t="s">
         <v>48</v>
@@ -5078,7 +5140,7 @@
       <c r="K34" s="12"/>
       <c r="L34" s="12"/>
     </row>
-    <row r="35" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="15" t="s">
         <v>48</v>
@@ -5100,7 +5162,7 @@
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
     </row>
-    <row r="36" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="15" t="s">
         <v>48</v>
@@ -5122,7 +5184,7 @@
       <c r="K36" s="12"/>
       <c r="L36" s="12"/>
     </row>
-    <row r="37" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="15" t="s">
         <v>48</v>
@@ -5144,7 +5206,7 @@
       <c r="K37" s="12"/>
       <c r="L37" s="12"/>
     </row>
-    <row r="38" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="15" t="s">
         <v>48</v>
@@ -5166,7 +5228,7 @@
       <c r="K38" s="12"/>
       <c r="L38" s="12"/>
     </row>
-    <row r="39" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="15" t="s">
         <v>48</v>
@@ -5188,7 +5250,7 @@
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
     </row>
-    <row r="40" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="15" t="s">
         <v>48</v>
@@ -5210,7 +5272,7 @@
       <c r="K40" s="12"/>
       <c r="L40" s="12"/>
     </row>
-    <row r="41" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="15" t="s">
         <v>48</v>
@@ -5232,7 +5294,7 @@
       <c r="K41" s="12"/>
       <c r="L41" s="12"/>
     </row>
-    <row r="42" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="15" t="s">
         <v>48</v>
@@ -5254,7 +5316,7 @@
       <c r="K42" s="12"/>
       <c r="L42" s="12"/>
     </row>
-    <row r="43" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="15" t="s">
         <v>48</v>
@@ -5276,7 +5338,7 @@
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
     </row>
-    <row r="44" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="15" t="s">
         <v>48</v>
@@ -5298,7 +5360,7 @@
       <c r="K44" s="12"/>
       <c r="L44" s="12"/>
     </row>
-    <row r="45" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
       <c r="B45" s="15" t="s">
         <v>48</v>
@@ -5320,7 +5382,7 @@
       <c r="K45" s="12"/>
       <c r="L45" s="12"/>
     </row>
-    <row r="46" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="15" t="s">
         <v>48</v>
@@ -5342,7 +5404,7 @@
       <c r="K46" s="12"/>
       <c r="L46" s="12"/>
     </row>
-    <row r="47" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="15" t="s">
         <v>48</v>
@@ -5364,7 +5426,7 @@
       <c r="K47" s="12"/>
       <c r="L47" s="12"/>
     </row>
-    <row r="48" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="15" t="s">
         <v>48</v>
@@ -5386,7 +5448,7 @@
       <c r="K48" s="12"/>
       <c r="L48" s="12"/>
     </row>
-    <row r="49" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="15" t="s">
         <v>48</v>
@@ -5408,7 +5470,7 @@
       <c r="K49" s="12"/>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="5"/>
       <c r="B50" s="15" t="s">
         <v>48</v>
@@ -5430,7 +5492,7 @@
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
     </row>
-    <row r="51" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="15" t="s">
         <v>48</v>
@@ -5452,7 +5514,7 @@
       <c r="K51" s="12"/>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="15" t="s">
         <v>48</v>
@@ -5474,7 +5536,7 @@
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
     </row>
-    <row r="53" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="15" t="s">
         <v>48</v>
@@ -5496,7 +5558,7 @@
       <c r="K53" s="12"/>
       <c r="L53" s="12"/>
     </row>
-    <row r="54" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="15" t="s">
         <v>48</v>
@@ -5518,7 +5580,7 @@
       <c r="K54" s="12"/>
       <c r="L54" s="12"/>
     </row>
-    <row r="55" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="15" t="s">
         <v>48</v>
@@ -5540,16 +5602,16 @@
       <c r="K55" s="12"/>
       <c r="L55" s="12"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>40</v>
@@ -5559,117 +5621,121 @@
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="J56" s="38">
-        <v>3</v>
+        <v>31</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="J56" s="38" t="s">
+        <v>182</v>
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="39"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="D57" s="25" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="J57" s="38">
-        <v>4</v>
+        <v>194</v>
+      </c>
+      <c r="J57" s="38" t="s">
+        <v>178</v>
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="39"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>158</v>
+        <v>203</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>204</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="J58" s="38">
-        <v>203</v>
-      </c>
-      <c r="K58" s="6"/>
-      <c r="L58" s="39"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+      <c r="J58" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="D59" s="25" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="J59" s="38">
-        <v>204</v>
-      </c>
-      <c r="K59" s="6"/>
-      <c r="L59" s="39"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+      <c r="J59" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>40</v>
@@ -5679,27 +5745,27 @@
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="J60" s="38" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="K60" s="6"/>
-      <c r="L60" s="39"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>167</v>
+        <v>235</v>
       </c>
       <c r="D61" s="25" t="s">
-        <v>168</v>
+        <v>236</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>40</v>
@@ -5709,18 +5775,18 @@
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I61" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="J61" s="38">
-        <v>5</v>
+        <v>237</v>
+      </c>
+      <c r="J61" s="38" t="s">
+        <v>238</v>
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="39"/>
     </row>
-    <row r="62" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="15" t="s">
         <v>48</v>
@@ -5742,72 +5808,78 @@
       <c r="K62" s="12"/>
       <c r="L62" s="12"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="E63" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="36" t="s">
-        <v>174</v>
-      </c>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-    </row>
-    <row r="64" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="F63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="J63" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="39"/>
+    </row>
+    <row r="64" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="6" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="J64" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="K64" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="J64" s="38">
+        <v>89</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>247</v>
+      </c>
       <c r="L64" s="39"/>
     </row>
-    <row r="65" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>40</v>
@@ -5815,20 +5887,24 @@
       <c r="F65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G65" s="6"/>
+      <c r="G65" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="H65" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="37" t="s">
-        <v>181</v>
+        <v>252</v>
       </c>
       <c r="J65" s="38" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="39"/>
-    </row>
-    <row r="66" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L65" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="15" t="s">
         <v>48</v>
@@ -5850,7 +5926,7 @@
       <c r="K66" s="12"/>
       <c r="L66" s="12"/>
     </row>
-    <row r="67" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="15" t="s">
         <v>48</v>
@@ -5872,7 +5948,7 @@
       <c r="K67" s="12"/>
       <c r="L67" s="12"/>
     </row>
-    <row r="68" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
         <v>21</v>
@@ -5906,37 +5982,41 @@
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D69" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="E69" s="6" t="s">
+      <c r="C69" s="59" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="E69" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="F69" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6" t="s">
+      <c r="F69" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="H69" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="I69" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="J69" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="K69" s="6"/>
-      <c r="L69" s="39"/>
-    </row>
-    <row r="70" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="J69" s="70">
+        <v>15</v>
+      </c>
+      <c r="K69" s="66" t="s">
+        <v>261</v>
+      </c>
+      <c r="L69" s="57"/>
+    </row>
+    <row r="70" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="15" t="s">
         <v>48</v>
@@ -5958,7 +6038,7 @@
       <c r="K70" s="12"/>
       <c r="L70" s="12"/>
     </row>
-    <row r="71" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="15" t="s">
         <v>48</v>
@@ -5980,7 +6060,7 @@
       <c r="K71" s="12"/>
       <c r="L71" s="12"/>
     </row>
-    <row r="72" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="5" t="s">
         <v>21</v>
@@ -6012,39 +6092,41 @@
       </c>
       <c r="L72" s="21"/>
     </row>
-    <row r="73" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="D73" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="E73" s="6" t="s">
+      <c r="C73" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="D73" s="63" t="s">
+        <v>263</v>
+      </c>
+      <c r="E73" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="J73" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="K73" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="L73" s="5"/>
-    </row>
-    <row r="74" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G73" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="H73" s="66" t="s">
+        <v>245</v>
+      </c>
+      <c r="I73" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="J73" s="70" t="s">
+        <v>265</v>
+      </c>
+      <c r="K73" s="66" t="s">
+        <v>261</v>
+      </c>
+      <c r="L73" s="66"/>
+    </row>
+    <row r="74" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5" t="s">
         <v>21</v>
@@ -6076,7 +6158,7 @@
       </c>
       <c r="L74" s="21"/>
     </row>
-    <row r="75" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="5" t="s">
         <v>21</v>
@@ -6108,39 +6190,35 @@
       </c>
       <c r="L75" s="21"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G76" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="H76" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I76" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="J76" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="L76" s="5"/>
-    </row>
-    <row r="77" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I76" s="37"/>
+      <c r="J76" s="41"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="39"/>
+    </row>
+    <row r="77" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="15" t="s">
         <v>48</v>
@@ -6162,61 +6240,71 @@
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D78" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="E78" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G78" s="5"/>
+      <c r="F78" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="6"/>
       <c r="H78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I78" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="I78" s="37"/>
+      <c r="J78" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D79" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="E79" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G79" s="5"/>
+      <c r="F79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="6"/>
       <c r="H79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I79" s="36"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
-    </row>
-    <row r="80" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I79" s="37"/>
+      <c r="J79" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="5" t="s">
         <v>21</v>
@@ -6248,97 +6336,103 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D81" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I81" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="J81" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="C81" s="59" t="s">
+        <v>278</v>
+      </c>
+      <c r="D81" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="E81" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="66"/>
+      <c r="H81" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="68"/>
+      <c r="J81" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="K81" s="66" t="s">
+        <v>274</v>
+      </c>
+      <c r="L81" s="66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I82" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="J82" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="K82" s="6"/>
-      <c r="L82" s="39"/>
-    </row>
-    <row r="83" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L82" s="8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D83" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I83" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="J83" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="K83" s="6"/>
-      <c r="L83" s="39"/>
-    </row>
-    <row r="84" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C83" s="59" t="s">
+        <v>282</v>
+      </c>
+      <c r="D83" s="65" t="s">
+        <v>283</v>
+      </c>
+      <c r="E83" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="66"/>
+      <c r="H83" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="68"/>
+      <c r="J83" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="K83" s="66" t="s">
+        <v>274</v>
+      </c>
+      <c r="L83" s="66" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="15" t="s">
         <v>48</v>
@@ -6360,16 +6454,16 @@
       <c r="K84" s="12"/>
       <c r="L84" s="12"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D85" s="25" t="s">
-        <v>244</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>291</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>15</v>
@@ -6379,20 +6473,18 @@
       </c>
       <c r="G85" s="6"/>
       <c r="H85" s="6" t="s">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="J85" s="38">
-        <v>89</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="L85" s="39"/>
-    </row>
-    <row r="86" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="J85" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="K85" s="6"/>
+      <c r="L85" s="5"/>
+    </row>
+    <row r="86" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="15" t="s">
         <v>48</v>
@@ -6414,41 +6506,37 @@
       <c r="K86" s="12"/>
       <c r="L86" s="12"/>
     </row>
-    <row r="87" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D87" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" s="6" t="s">
+      <c r="C87" s="59" t="s">
+        <v>347</v>
+      </c>
+      <c r="D87" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="E87" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I87" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="J87" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="K87" s="6"/>
-      <c r="L87" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G87" s="66"/>
+      <c r="H87" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="J87" s="70" t="s">
+        <v>293</v>
+      </c>
+      <c r="K87" s="66"/>
+      <c r="L87" s="73"/>
+    </row>
+    <row r="88" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="5"/>
       <c r="B88" s="5" t="s">
         <v>21</v>
@@ -6480,103 +6568,103 @@
       </c>
       <c r="L88" s="19"/>
     </row>
-    <row r="89" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A89" s="45"/>
       <c r="B89" s="45" t="s">
         <v>12</v>
       </c>
       <c r="C89" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="D89" s="47" t="s">
-        <v>259</v>
+        <v>349</v>
+      </c>
+      <c r="D89" s="51" t="s">
+        <v>350</v>
       </c>
       <c r="E89" s="48" t="s">
         <v>15</v>
       </c>
       <c r="F89" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="G89" s="48"/>
+      <c r="H89" s="48" t="s">
+        <v>245</v>
+      </c>
+      <c r="I89" s="49" t="s">
+        <v>292</v>
+      </c>
+      <c r="J89" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="K89" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="L89" s="48"/>
+    </row>
+    <row r="90" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="45"/>
+      <c r="B90" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="60" t="s">
+        <v>355</v>
+      </c>
+      <c r="D90" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="E90" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="G89" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="H89" s="48" t="s">
+      <c r="G90" s="67"/>
+      <c r="H90" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="I89" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="J89" s="50">
-        <v>15</v>
-      </c>
-      <c r="K89" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="L89" s="45"/>
-    </row>
-    <row r="90" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A90" s="45"/>
-      <c r="B90" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="46" t="s">
-        <v>262</v>
-      </c>
-      <c r="D90" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="E90" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="H90" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="I90" s="49" t="s">
-        <v>264</v>
-      </c>
-      <c r="J90" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="K90" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="L90" s="48"/>
-    </row>
-    <row r="91" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="I90" s="69"/>
+      <c r="J90" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="K90" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="L90" s="58"/>
+    </row>
+    <row r="91" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="D91" s="25" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G91" s="6"/>
       <c r="H91" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I91" s="37"/>
-      <c r="J91" s="41"/>
-      <c r="K91" s="6"/>
-      <c r="L91" s="39"/>
-    </row>
-    <row r="92" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I91" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J91" s="38" t="s">
+        <v>361</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="15" t="s">
         <v>48</v>
@@ -6598,7 +6686,7 @@
       <c r="K92" s="12"/>
       <c r="L92" s="12"/>
     </row>
-    <row r="93" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="15" t="s">
         <v>48</v>
@@ -6620,16 +6708,16 @@
       <c r="K93" s="12"/>
       <c r="L93" s="12"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="D94" s="27" t="s">
-        <v>273</v>
+        <v>367</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>368</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>15</v>
@@ -6639,61 +6727,61 @@
       </c>
       <c r="G94" s="6"/>
       <c r="H94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="I94" s="37" t="s">
+        <v>369</v>
+      </c>
       <c r="J94" s="38" t="s">
-        <v>24</v>
+        <v>370</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="5"/>
       <c r="B95" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="D95" s="27" t="s">
-        <v>277</v>
+        <v>380</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>381</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G95" s="6"/>
       <c r="H95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I95" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="I95" s="37" t="s">
+        <v>292</v>
+      </c>
       <c r="J95" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+      <c r="K95" s="6"/>
+      <c r="L95" s="5"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="45"/>
       <c r="B96" s="45" t="s">
         <v>12</v>
       </c>
       <c r="C96" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="D96" s="52" t="s">
-        <v>279</v>
+        <v>388</v>
+      </c>
+      <c r="D96" s="51" t="s">
+        <v>389</v>
       </c>
       <c r="E96" s="48" t="s">
         <v>15</v>
@@ -6703,84 +6791,84 @@
       </c>
       <c r="G96" s="48"/>
       <c r="H96" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="I96" s="49"/>
+        <v>245</v>
+      </c>
+      <c r="I96" s="49" t="s">
+        <v>264</v>
+      </c>
       <c r="J96" s="50" t="s">
-        <v>24</v>
+        <v>265</v>
       </c>
       <c r="K96" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="L96" s="48" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+      <c r="L96" s="48"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="5"/>
       <c r="B97" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="E97" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="E97" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F97" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8" t="s">
+      <c r="G97" s="6"/>
+      <c r="H97" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="I97" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="J97" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="45"/>
+      <c r="B98" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" s="60" t="s">
+        <v>396</v>
+      </c>
+      <c r="D98" s="64" t="s">
+        <v>397</v>
+      </c>
+      <c r="E98" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" s="67" t="s">
+        <v>398</v>
+      </c>
+      <c r="G98" s="67"/>
+      <c r="H98" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="L97" s="8" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A98" s="45"/>
-      <c r="B98" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="D98" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="E98" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="49"/>
-      <c r="J98" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="K98" s="48" t="s">
-        <v>274</v>
-      </c>
-      <c r="L98" s="48" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I98" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="J98" s="71">
+        <v>66</v>
+      </c>
+      <c r="K98" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="L98" s="58"/>
+    </row>
+    <row r="99" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="5"/>
       <c r="B99" s="15" t="s">
         <v>48</v>
@@ -6802,7 +6890,7 @@
       <c r="K99" s="12"/>
       <c r="L99" s="12"/>
     </row>
-    <row r="100" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A100" s="5"/>
       <c r="B100" s="15" t="s">
         <v>48</v>
@@ -6824,7 +6912,7 @@
       <c r="K100" s="12"/>
       <c r="L100" s="12"/>
     </row>
-    <row r="101" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="5"/>
       <c r="B101" s="15" t="s">
         <v>48</v>
@@ -6846,16 +6934,16 @@
       <c r="K101" s="12"/>
       <c r="L101" s="12"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="5"/>
       <c r="B102" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D102" s="28" t="s">
-        <v>291</v>
+        <v>403</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>404</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>15</v>
@@ -6863,20 +6951,26 @@
       <c r="F102" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G102" s="6"/>
+      <c r="G102" s="6" t="s">
+        <v>188</v>
+      </c>
       <c r="H102" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I102" s="37" t="s">
-        <v>292</v>
+        <v>405</v>
       </c>
       <c r="J102" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="K102" s="6"/>
-      <c r="L102" s="5"/>
-    </row>
-    <row r="103" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="L102" s="39" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="5"/>
       <c r="B103" s="5" t="s">
         <v>21</v>
@@ -6908,7 +7002,7 @@
       </c>
       <c r="L103" s="12"/>
     </row>
-    <row r="104" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A104" s="5"/>
       <c r="B104" s="5" t="s">
         <v>21</v>
@@ -6940,7 +7034,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="105" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A105" s="5"/>
       <c r="B105" s="5" t="s">
         <v>21</v>
@@ -6972,7 +7066,7 @@
       </c>
       <c r="L105" s="19"/>
     </row>
-    <row r="106" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="5"/>
       <c r="B106" s="5" t="s">
         <v>21</v>
@@ -7004,7 +7098,7 @@
       </c>
       <c r="L106" s="19"/>
     </row>
-    <row r="107" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="5"/>
       <c r="B107" s="5" t="s">
         <v>21</v>
@@ -7036,7 +7130,7 @@
       </c>
       <c r="L107" s="19"/>
     </row>
-    <row r="108" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="5"/>
       <c r="B108" s="5" t="s">
         <v>21</v>
@@ -7068,7 +7162,7 @@
       </c>
       <c r="L108" s="19"/>
     </row>
-    <row r="109" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="5"/>
       <c r="B109" s="5" t="s">
         <v>21</v>
@@ -7100,7 +7194,7 @@
       </c>
       <c r="L109" s="19"/>
     </row>
-    <row r="110" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="5"/>
       <c r="B110" s="5" t="s">
         <v>21</v>
@@ -7132,7 +7226,7 @@
       </c>
       <c r="L110" s="19"/>
     </row>
-    <row r="111" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A111" s="5"/>
       <c r="B111" s="5" t="s">
         <v>21</v>
@@ -7164,7 +7258,7 @@
       </c>
       <c r="L111" s="19"/>
     </row>
-    <row r="112" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="5"/>
       <c r="B112" s="5" t="s">
         <v>21</v>
@@ -7196,7 +7290,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="113" spans="1:12" customFormat="1" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" s="5"/>
       <c r="B113" s="5" t="s">
         <v>21</v>
@@ -7228,7 +7322,7 @@
       </c>
       <c r="L113" s="19"/>
     </row>
-    <row r="114" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A114" s="5"/>
       <c r="B114" s="5" t="s">
         <v>21</v>
@@ -7258,7 +7352,7 @@
       <c r="K114" s="19"/>
       <c r="L114" s="21"/>
     </row>
-    <row r="115" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="5"/>
       <c r="B115" s="5" t="s">
         <v>21</v>
@@ -7288,7 +7382,7 @@
       <c r="K115" s="19"/>
       <c r="L115" s="19"/>
     </row>
-    <row r="116" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="5"/>
       <c r="B116" s="5" t="s">
         <v>21</v>
@@ -7320,7 +7414,7 @@
       </c>
       <c r="L116" s="19"/>
     </row>
-    <row r="117" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="5"/>
       <c r="B117" s="15" t="s">
         <v>48</v>
@@ -7342,7 +7436,7 @@
       <c r="K117" s="12"/>
       <c r="L117" s="12"/>
     </row>
-    <row r="118" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A118" s="5"/>
       <c r="B118" s="15" t="s">
         <v>48</v>
@@ -7364,7 +7458,7 @@
       <c r="K118" s="12"/>
       <c r="L118" s="12"/>
     </row>
-    <row r="119" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A119" s="5"/>
       <c r="B119" s="15" t="s">
         <v>48</v>
@@ -7386,7 +7480,7 @@
       <c r="K119" s="12"/>
       <c r="L119" s="12"/>
     </row>
-    <row r="120" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="5"/>
       <c r="B120" s="15" t="s">
         <v>48</v>
@@ -7408,7 +7502,7 @@
       <c r="K120" s="12"/>
       <c r="L120" s="12"/>
     </row>
-    <row r="121" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A121" s="5"/>
       <c r="B121" s="15" t="s">
         <v>48</v>
@@ -7430,7 +7524,7 @@
       <c r="K121" s="12"/>
       <c r="L121" s="12"/>
     </row>
-    <row r="122" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A122" s="5"/>
       <c r="B122" s="15" t="s">
         <v>48</v>
@@ -7452,7 +7546,7 @@
       <c r="K122" s="12"/>
       <c r="L122" s="12"/>
     </row>
-    <row r="123" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A123" s="5"/>
       <c r="B123" s="5" t="s">
         <v>21</v>
@@ -7482,69 +7576,73 @@
       <c r="K123" s="19"/>
       <c r="L123" s="21"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="45"/>
-      <c r="B124" s="45" t="s">
+      <c r="B124" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C124" s="46" t="s">
-        <v>347</v>
-      </c>
-      <c r="D124" s="51" t="s">
-        <v>348</v>
-      </c>
-      <c r="E124" s="48" t="s">
+      <c r="C124" s="60" t="s">
+        <v>407</v>
+      </c>
+      <c r="D124" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="E124" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F124" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="G124" s="48"/>
-      <c r="H124" s="48" t="s">
+      <c r="F124" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="67" t="s">
+        <v>409</v>
+      </c>
+      <c r="H124" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="I124" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="J124" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="K124" s="48"/>
-      <c r="L124" s="53"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I124" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="J124" s="71">
+        <v>108</v>
+      </c>
+      <c r="K124" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="L124" s="58"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="45"/>
-      <c r="B125" s="45" t="s">
+      <c r="B125" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C125" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="D125" s="51" t="s">
-        <v>350</v>
-      </c>
-      <c r="E125" s="48" t="s">
+      <c r="C125" s="60" t="s">
+        <v>412</v>
+      </c>
+      <c r="D125" s="62" t="s">
+        <v>413</v>
+      </c>
+      <c r="E125" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F125" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="G125" s="48"/>
-      <c r="H125" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="I125" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="J125" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="K125" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="L125" s="48"/>
-    </row>
-    <row r="126" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F125" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="67"/>
+      <c r="H125" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="I125" s="69" t="s">
+        <v>410</v>
+      </c>
+      <c r="J125" s="71">
+        <v>108</v>
+      </c>
+      <c r="K125" s="67" t="s">
+        <v>411</v>
+      </c>
+      <c r="L125" s="58"/>
+    </row>
+    <row r="126" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A126" s="5"/>
       <c r="B126" s="15" t="s">
         <v>48</v>
@@ -7566,7 +7664,7 @@
       <c r="K126" s="12"/>
       <c r="L126" s="12"/>
     </row>
-    <row r="127" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A127" s="5"/>
       <c r="B127" s="5" t="s">
         <v>21</v>
@@ -7598,16 +7696,16 @@
       </c>
       <c r="L127" s="12"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="5"/>
       <c r="B128" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D128" s="28" t="s">
-        <v>356</v>
+        <v>414</v>
+      </c>
+      <c r="D128" s="25" t="s">
+        <v>415</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>15</v>
@@ -7617,27 +7715,29 @@
       </c>
       <c r="G128" s="6"/>
       <c r="H128" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I128" s="37"/>
-      <c r="J128" s="38" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="I128" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="J128" s="38">
+        <v>108</v>
       </c>
       <c r="K128" s="6" t="s">
-        <v>357</v>
+        <v>411</v>
       </c>
       <c r="L128" s="5"/>
     </row>
-    <row r="129" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A129" s="5"/>
       <c r="B129" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="D129" s="25" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>15</v>
@@ -7649,20 +7749,16 @@
       <c r="H129" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I129" s="37" t="s">
-        <v>360</v>
-      </c>
+      <c r="I129" s="37"/>
       <c r="J129" s="38" t="s">
-        <v>361</v>
+        <v>24</v>
       </c>
       <c r="K129" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="L129" s="6" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+      <c r="L129" s="5"/>
+    </row>
+    <row r="130" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="5"/>
       <c r="B130" s="5" t="s">
         <v>21</v>
@@ -7696,41 +7792,43 @@
         <v>363</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="69" x14ac:dyDescent="0.3">
       <c r="A131" s="5"/>
       <c r="B131" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="D131" s="25" t="s">
-        <v>368</v>
+        <v>447</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G131" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="G131" s="6" t="s">
+        <v>448</v>
+      </c>
       <c r="H131" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I131" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="J131" s="38" t="s">
-        <v>370</v>
+        <v>449</v>
+      </c>
+      <c r="J131" s="38">
+        <v>49</v>
       </c>
       <c r="K131" s="6" t="s">
-        <v>362</v>
+        <v>450</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A132" s="5"/>
       <c r="B132" s="15" t="s">
         <v>48</v>
@@ -7752,7 +7850,7 @@
       <c r="K132" s="12"/>
       <c r="L132" s="12"/>
     </row>
-    <row r="133" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A133" s="5"/>
       <c r="B133" s="15" t="s">
         <v>48</v>
@@ -7774,7 +7872,7 @@
       <c r="K133" s="12"/>
       <c r="L133" s="12"/>
     </row>
-    <row r="134" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A134" s="5"/>
       <c r="B134" s="15" t="s">
         <v>48</v>
@@ -7796,7 +7894,7 @@
       <c r="K134" s="12"/>
       <c r="L134" s="12"/>
     </row>
-    <row r="135" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A135" s="5"/>
       <c r="B135" s="5" t="s">
         <v>21</v>
@@ -7826,37 +7924,39 @@
       <c r="K135" s="12"/>
       <c r="L135" s="19"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="5"/>
       <c r="B136" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C136" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="D136" s="28" t="s">
-        <v>381</v>
+      <c r="C136" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>589</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G136" s="6"/>
       <c r="H136" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I136" s="37" t="s">
-        <v>292</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I136" s="37"/>
       <c r="J136" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="K136" s="6"/>
-      <c r="L136" s="5"/>
-    </row>
-    <row r="137" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="K136" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="L136" s="6" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A137" s="5"/>
       <c r="B137" s="15" t="s">
         <v>48</v>
@@ -7878,7 +7978,7 @@
       <c r="K137" s="12"/>
       <c r="L137" s="12"/>
     </row>
-    <row r="138" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A138" s="5"/>
       <c r="B138" s="15" t="s">
         <v>48</v>
@@ -7900,7 +8000,7 @@
       <c r="K138" s="12"/>
       <c r="L138" s="12"/>
     </row>
-    <row r="139" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A139" s="5"/>
       <c r="B139" s="5" t="s">
         <v>21</v>
@@ -7932,39 +8032,35 @@
       </c>
       <c r="L139" s="12"/>
     </row>
-    <row r="140" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A140" s="45"/>
-      <c r="B140" s="45" t="s">
+      <c r="B140" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C140" s="46" t="s">
-        <v>388</v>
-      </c>
-      <c r="D140" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="E140" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G140" s="48"/>
-      <c r="H140" s="48" t="s">
-        <v>245</v>
-      </c>
-      <c r="I140" s="49" t="s">
-        <v>264</v>
-      </c>
-      <c r="J140" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="K140" s="48" t="s">
-        <v>261</v>
-      </c>
-      <c r="L140" s="48"/>
-    </row>
-    <row r="141" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C140" s="60" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D140" s="62" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E140" s="67" t="s">
+        <v>402</v>
+      </c>
+      <c r="F140" s="67" t="s">
+        <v>398</v>
+      </c>
+      <c r="G140" s="67"/>
+      <c r="H140" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="69"/>
+      <c r="J140" s="71">
+        <v>127</v>
+      </c>
+      <c r="K140" s="67"/>
+      <c r="L140" s="72"/>
+    </row>
+    <row r="141" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A141" s="5"/>
       <c r="B141" s="5" t="s">
         <v>21</v>
@@ -7996,16 +8092,16 @@
       </c>
       <c r="L141" s="19"/>
     </row>
-    <row r="142" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A142" s="5"/>
       <c r="B142" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="D142" s="25" t="s">
-        <v>394</v>
+        <v>1051</v>
+      </c>
+      <c r="D142" s="28" t="s">
+        <v>1052</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>15</v>
@@ -8015,52 +8111,50 @@
       </c>
       <c r="G142" s="6"/>
       <c r="H142" s="6" t="s">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="I142" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="J142" s="38" t="s">
-        <v>265</v>
+        <v>1053</v>
+      </c>
+      <c r="J142" s="38">
+        <v>66</v>
       </c>
       <c r="K142" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="L142" s="6"/>
-    </row>
-    <row r="143" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>1054</v>
+      </c>
+      <c r="L142" s="5"/>
+    </row>
+    <row r="143" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A143" s="5"/>
       <c r="B143" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="D143" s="28" t="s">
-        <v>397</v>
+        <v>1057</v>
+      </c>
+      <c r="D143" s="25" t="s">
+        <v>1058</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>398</v>
+        <v>16</v>
       </c>
       <c r="G143" s="6"/>
       <c r="H143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I143" s="37" t="s">
-        <v>399</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I143" s="37"/>
       <c r="J143" s="38">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="K143" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="L143" s="5"/>
-    </row>
-    <row r="144" spans="1:12" customFormat="1" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
+        <v>1059</v>
+      </c>
+      <c r="L143" s="6"/>
+    </row>
+    <row r="144" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A144" s="5"/>
       <c r="B144" s="5" t="s">
         <v>21</v>
@@ -8090,52 +8184,46 @@
       <c r="K144" s="19"/>
       <c r="L144" s="12"/>
     </row>
-    <row r="145" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A145" s="5"/>
       <c r="B145" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>403</v>
+        <v>1060</v>
       </c>
       <c r="D145" s="25" t="s">
-        <v>404</v>
+        <v>1061</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G145" s="6" t="s">
-        <v>188</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G145" s="6"/>
       <c r="H145" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I145" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="J145" s="38" t="s">
-        <v>189</v>
+      <c r="I145" s="37"/>
+      <c r="J145" s="38">
+        <v>159</v>
       </c>
       <c r="K145" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="L145" s="39" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+        <v>1062</v>
+      </c>
+      <c r="L145" s="6"/>
+    </row>
+    <row r="146" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A146" s="5"/>
       <c r="B146" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>407</v>
+        <v>1063</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>408</v>
+        <v>1064</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>15</v>
@@ -8143,33 +8231,29 @@
       <c r="F146" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G146" s="6" t="s">
-        <v>409</v>
-      </c>
+      <c r="G146" s="6"/>
       <c r="H146" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I146" s="37" t="s">
-        <v>410</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I146" s="37"/>
       <c r="J146" s="38">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="L146" s="5"/>
-    </row>
-    <row r="147" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>1059</v>
+      </c>
+      <c r="L146" s="6"/>
+    </row>
+    <row r="147" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A147" s="5"/>
       <c r="B147" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>412</v>
+        <v>1065</v>
       </c>
       <c r="D147" s="25" t="s">
-        <v>413</v>
+        <v>1066</v>
       </c>
       <c r="E147" s="6" t="s">
         <v>15</v>
@@ -8179,82 +8263,70 @@
       </c>
       <c r="G147" s="6"/>
       <c r="H147" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I147" s="37" t="s">
-        <v>410</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I147" s="37"/>
       <c r="J147" s="38">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>411</v>
+        <v>1062</v>
       </c>
       <c r="L147" s="5"/>
     </row>
-    <row r="148" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A148" s="5"/>
-      <c r="B148" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="D148" s="25" t="s">
-        <v>415</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I148" s="37" t="s">
-        <v>410</v>
-      </c>
-      <c r="J148" s="38">
-        <v>108</v>
-      </c>
-      <c r="K148" s="6" t="s">
-        <v>411</v>
-      </c>
+      <c r="B148" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I148" s="36"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
       <c r="L148" s="5"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="5"/>
-      <c r="B149" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="D149" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6" t="s">
+      <c r="B149" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D149" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E149" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I149" s="37"/>
-      <c r="J149" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K149" s="6" t="s">
-        <v>418</v>
-      </c>
+      <c r="I149" s="36"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
       <c r="L149" s="5"/>
     </row>
-    <row r="150" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A150" s="5"/>
       <c r="B150" s="15" t="s">
         <v>48</v>
@@ -8276,7 +8348,7 @@
       <c r="K150" s="12"/>
       <c r="L150" s="12"/>
     </row>
-    <row r="151" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A151" s="5"/>
       <c r="B151" s="5" t="s">
         <v>21</v>
@@ -8308,7 +8380,7 @@
       </c>
       <c r="L151" s="19"/>
     </row>
-    <row r="152" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A152" s="5"/>
       <c r="B152" s="5" t="s">
         <v>21</v>
@@ -8342,7 +8414,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" s="5"/>
       <c r="B153" s="5" t="s">
         <v>21</v>
@@ -8376,7 +8448,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="154" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A154" s="5"/>
       <c r="B154" s="5" t="s">
         <v>21</v>
@@ -8410,7 +8482,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="155" spans="1:12" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" s="5"/>
       <c r="B155" s="5" t="s">
         <v>21</v>
@@ -8444,7 +8516,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="156" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="5"/>
       <c r="B156" s="15" t="s">
         <v>48</v>
@@ -8466,102 +8538,96 @@
       <c r="K156" s="12"/>
       <c r="L156" s="12"/>
     </row>
-    <row r="157" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A157" s="5"/>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>436</v>
+        <v>34</v>
       </c>
       <c r="D157" s="24" t="s">
-        <v>437</v>
-      </c>
-      <c r="E157" s="55" t="s">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="E157" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G157" s="5"/>
       <c r="H157" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I157" s="37" t="s">
-        <v>438</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I157" s="36"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
       <c r="L157" s="5"/>
     </row>
-    <row r="158" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A158" s="5"/>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>439</v>
+        <v>36</v>
       </c>
       <c r="D158" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="E158" s="55" t="s">
-        <v>15</v>
+        <v>37</v>
+      </c>
+      <c r="E158" s="53" t="s">
+        <v>29</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I158" s="37" t="s">
-        <v>438</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I158" s="36"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
     </row>
-    <row r="159" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A159" s="5"/>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>441</v>
+        <v>45</v>
       </c>
       <c r="D159" s="24" t="s">
-        <v>442</v>
-      </c>
-      <c r="E159" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E159" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G159" s="5"/>
-      <c r="H159" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I159" s="37" t="s">
-        <v>443</v>
-      </c>
+      <c r="H159" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I159" s="36"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
       <c r="L159" s="5"/>
     </row>
-    <row r="160" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A160" s="5"/>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>444</v>
+        <v>60</v>
       </c>
       <c r="D160" s="24" t="s">
-        <v>445</v>
-      </c>
-      <c r="E160" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="E160" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F160" s="2" t="s">
@@ -8571,76 +8637,70 @@
       <c r="H160" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I160" s="37" t="s">
-        <v>443</v>
+      <c r="I160" s="36" t="s">
+        <v>62</v>
       </c>
       <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
+      <c r="K160" s="40" t="s">
+        <v>63</v>
+      </c>
       <c r="L160" s="5"/>
     </row>
-    <row r="161" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A161" s="5"/>
       <c r="B161" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C161" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D161" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F161" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G161" s="6" t="s">
-        <v>448</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C161" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D161" s="56" t="s">
+        <v>77</v>
+      </c>
+      <c r="E161" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G161" s="5"/>
       <c r="H161" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I161" s="37" t="s">
-        <v>449</v>
-      </c>
-      <c r="J161" s="38">
-        <v>49</v>
-      </c>
-      <c r="K161" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="L161" s="6" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I161" s="36"/>
+      <c r="J161" s="5"/>
+      <c r="K161" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L161" s="5"/>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="5"/>
       <c r="B162" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>452</v>
+        <v>172</v>
       </c>
       <c r="D162" s="24" t="s">
-        <v>453</v>
-      </c>
-      <c r="E162" s="55" t="s">
-        <v>15</v>
+        <v>173</v>
+      </c>
+      <c r="E162" s="53" t="s">
+        <v>40</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G162" s="5"/>
-      <c r="H162" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I162" s="36"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="36" t="s">
+        <v>174</v>
+      </c>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
       <c r="L162" s="5"/>
     </row>
-    <row r="163" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="5"/>
       <c r="B163" s="15" t="s">
         <v>48</v>
@@ -8662,7 +8722,7 @@
       <c r="K163" s="12"/>
       <c r="L163" s="12"/>
     </row>
-    <row r="164" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="5"/>
       <c r="B164" s="15" t="s">
         <v>48</v>
@@ -8684,7 +8744,7 @@
       <c r="K164" s="12"/>
       <c r="L164" s="12"/>
     </row>
-    <row r="165" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="5"/>
       <c r="B165" s="15" t="s">
         <v>48</v>
@@ -8706,7 +8766,7 @@
       <c r="K165" s="12"/>
       <c r="L165" s="12"/>
     </row>
-    <row r="166" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="5"/>
       <c r="B166" s="15" t="s">
         <v>48</v>
@@ -8728,18 +8788,18 @@
       <c r="K166" s="12"/>
       <c r="L166" s="12"/>
     </row>
-    <row r="167" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5"/>
       <c r="B167" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>462</v>
+        <v>222</v>
       </c>
       <c r="D167" s="24" t="s">
-        <v>463</v>
-      </c>
-      <c r="E167" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="E167" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F167" s="2" t="s">
@@ -8747,16 +8807,16 @@
       </c>
       <c r="G167" s="5"/>
       <c r="H167" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I167" s="36" t="s">
-        <v>62</v>
+        <v>224</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
     </row>
-    <row r="168" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="5"/>
       <c r="B168" s="15" t="s">
         <v>48</v>
@@ -8778,7 +8838,7 @@
       <c r="K168" s="12"/>
       <c r="L168" s="12"/>
     </row>
-    <row r="169" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="5"/>
       <c r="B169" s="15" t="s">
         <v>48</v>
@@ -8800,7 +8860,7 @@
       <c r="K169" s="12"/>
       <c r="L169" s="12"/>
     </row>
-    <row r="170" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="5"/>
       <c r="B170" s="15" t="s">
         <v>48</v>
@@ -8822,7 +8882,7 @@
       <c r="K170" s="12"/>
       <c r="L170" s="12"/>
     </row>
-    <row r="171" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="5"/>
       <c r="B171" s="15" t="s">
         <v>48</v>
@@ -8844,7 +8904,7 @@
       <c r="K171" s="12"/>
       <c r="L171" s="12"/>
     </row>
-    <row r="172" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="5"/>
       <c r="B172" s="15" t="s">
         <v>48</v>
@@ -8866,7 +8926,7 @@
       <c r="K172" s="12"/>
       <c r="L172" s="12"/>
     </row>
-    <row r="173" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="5"/>
       <c r="B173" s="15" t="s">
         <v>48</v>
@@ -8888,7 +8948,7 @@
       <c r="K173" s="12"/>
       <c r="L173" s="12"/>
     </row>
-    <row r="174" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="5"/>
       <c r="B174" s="15" t="s">
         <v>48</v>
@@ -8910,7 +8970,7 @@
       <c r="K174" s="12"/>
       <c r="L174" s="12"/>
     </row>
-    <row r="175" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="5"/>
       <c r="B175" s="15" t="s">
         <v>48</v>
@@ -8932,7 +8992,7 @@
       <c r="K175" s="12"/>
       <c r="L175" s="12"/>
     </row>
-    <row r="176" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="5"/>
       <c r="B176" s="15" t="s">
         <v>48</v>
@@ -8954,7 +9014,7 @@
       <c r="K176" s="12"/>
       <c r="L176" s="12"/>
     </row>
-    <row r="177" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="5"/>
       <c r="B177" s="15" t="s">
         <v>48</v>
@@ -8976,7 +9036,7 @@
       <c r="K177" s="12"/>
       <c r="L177" s="12"/>
     </row>
-    <row r="178" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="5"/>
       <c r="B178" s="15" t="s">
         <v>48</v>
@@ -8998,7 +9058,7 @@
       <c r="K178" s="12"/>
       <c r="L178" s="12"/>
     </row>
-    <row r="179" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="5"/>
       <c r="B179" s="15" t="s">
         <v>48</v>
@@ -9020,7 +9080,7 @@
       <c r="K179" s="12"/>
       <c r="L179" s="12"/>
     </row>
-    <row r="180" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="5"/>
       <c r="B180" s="15" t="s">
         <v>48</v>
@@ -9042,7 +9102,7 @@
       <c r="K180" s="12"/>
       <c r="L180" s="12"/>
     </row>
-    <row r="181" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A181" s="5"/>
       <c r="B181" s="15" t="s">
         <v>48</v>
@@ -9064,7 +9124,7 @@
       <c r="K181" s="12"/>
       <c r="L181" s="12"/>
     </row>
-    <row r="182" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A182" s="5"/>
       <c r="B182" s="15" t="s">
         <v>48</v>
@@ -9086,7 +9146,7 @@
       <c r="K182" s="12"/>
       <c r="L182" s="12"/>
     </row>
-    <row r="183" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A183" s="5"/>
       <c r="B183" s="15" t="s">
         <v>48</v>
@@ -9108,7 +9168,7 @@
       <c r="K183" s="12"/>
       <c r="L183" s="12"/>
     </row>
-    <row r="184" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A184" s="5"/>
       <c r="B184" s="15" t="s">
         <v>48</v>
@@ -9130,7 +9190,7 @@
       <c r="K184" s="12"/>
       <c r="L184" s="12"/>
     </row>
-    <row r="185" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A185" s="5"/>
       <c r="B185" s="15" t="s">
         <v>48</v>
@@ -9152,7 +9212,7 @@
       <c r="K185" s="12"/>
       <c r="L185" s="12"/>
     </row>
-    <row r="186" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A186" s="5"/>
       <c r="B186" s="15" t="s">
         <v>48</v>
@@ -9174,7 +9234,7 @@
       <c r="K186" s="12"/>
       <c r="L186" s="12"/>
     </row>
-    <row r="187" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A187" s="5"/>
       <c r="B187" s="15" t="s">
         <v>48</v>
@@ -9196,18 +9256,18 @@
       <c r="K187" s="12"/>
       <c r="L187" s="12"/>
     </row>
-    <row r="188" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A188" s="5"/>
       <c r="B188" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>504</v>
+        <v>225</v>
       </c>
       <c r="D188" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="E188" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="E188" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F188" s="2" t="s">
@@ -9217,68 +9277,68 @@
       <c r="H188" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I188" s="36" t="s">
-        <v>62</v>
-      </c>
+      <c r="I188" s="36"/>
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
       <c r="L188" s="5"/>
     </row>
-    <row r="189" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="5"/>
       <c r="B189" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>506</v>
+        <v>436</v>
       </c>
       <c r="D189" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="E189" s="55" t="s">
+        <v>437</v>
+      </c>
+      <c r="E189" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G189" s="5"/>
-      <c r="H189" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I189" s="36" t="s">
-        <v>62</v>
+      <c r="H189" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I189" s="37" t="s">
+        <v>438</v>
       </c>
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
       <c r="L189" s="5"/>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="5"/>
       <c r="B190" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="D190" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="E190" s="10" t="s">
-        <v>40</v>
+        <v>440</v>
+      </c>
+      <c r="E190" s="53" t="s">
+        <v>15</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G190" s="5"/>
-      <c r="H190" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I190" s="36"/>
+      <c r="H190" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I190" s="37" t="s">
+        <v>438</v>
+      </c>
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
       <c r="L190" s="5"/>
     </row>
-    <row r="191" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A191" s="5"/>
       <c r="B191" s="15" t="s">
         <v>48</v>
@@ -9300,59 +9360,63 @@
       <c r="K191" s="12"/>
       <c r="L191" s="12"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="5"/>
       <c r="B192" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>512</v>
+        <v>441</v>
       </c>
       <c r="D192" s="24" t="s">
-        <v>513</v>
-      </c>
-      <c r="E192" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="E192" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G192" s="5"/>
-      <c r="H192" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I192" s="36"/>
+      <c r="H192" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I192" s="37" t="s">
+        <v>443</v>
+      </c>
       <c r="J192" s="5"/>
       <c r="K192" s="5"/>
       <c r="L192" s="5"/>
     </row>
-    <row r="193" spans="1:12" ht="1.1499999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="1.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="5"/>
       <c r="B193" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>514</v>
+        <v>444</v>
       </c>
       <c r="D193" s="24" t="s">
-        <v>515</v>
-      </c>
-      <c r="E193" s="55" t="s">
+        <v>445</v>
+      </c>
+      <c r="E193" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>47</v>
       </c>
       <c r="G193" s="5"/>
-      <c r="H193" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I193" s="36"/>
+      <c r="H193" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" s="37" t="s">
+        <v>443</v>
+      </c>
       <c r="J193" s="5"/>
       <c r="K193" s="5"/>
       <c r="L193" s="5"/>
     </row>
-    <row r="194" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A194" s="5"/>
       <c r="B194" s="15" t="s">
         <v>48</v>
@@ -9374,7 +9438,7 @@
       <c r="K194" s="12"/>
       <c r="L194" s="12"/>
     </row>
-    <row r="195" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A195" s="5"/>
       <c r="B195" s="15" t="s">
         <v>48</v>
@@ -9396,7 +9460,7 @@
       <c r="K195" s="12"/>
       <c r="L195" s="12"/>
     </row>
-    <row r="196" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A196" s="5"/>
       <c r="B196" s="15" t="s">
         <v>48</v>
@@ -9418,7 +9482,7 @@
       <c r="K196" s="12"/>
       <c r="L196" s="12"/>
     </row>
-    <row r="197" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A197" s="5"/>
       <c r="B197" s="15" t="s">
         <v>48</v>
@@ -9440,7 +9504,7 @@
       <c r="K197" s="12"/>
       <c r="L197" s="12"/>
     </row>
-    <row r="198" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A198" s="5"/>
       <c r="B198" s="15" t="s">
         <v>48</v>
@@ -9462,7 +9526,7 @@
       <c r="K198" s="12"/>
       <c r="L198" s="12"/>
     </row>
-    <row r="199" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A199" s="5"/>
       <c r="B199" s="15" t="s">
         <v>48</v>
@@ -9484,7 +9548,7 @@
       <c r="K199" s="12"/>
       <c r="L199" s="12"/>
     </row>
-    <row r="200" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A200" s="5"/>
       <c r="B200" s="15" t="s">
         <v>48</v>
@@ -9506,7 +9570,7 @@
       <c r="K200" s="12"/>
       <c r="L200" s="12"/>
     </row>
-    <row r="201" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A201" s="5"/>
       <c r="B201" s="15" t="s">
         <v>48</v>
@@ -9528,18 +9592,18 @@
       <c r="K201" s="12"/>
       <c r="L201" s="12"/>
     </row>
-    <row r="202" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="0.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="5"/>
       <c r="B202" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>532</v>
+        <v>452</v>
       </c>
       <c r="D202" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="E202" s="55" t="s">
+        <v>453</v>
+      </c>
+      <c r="E202" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F202" s="2" t="s">
@@ -9547,14 +9611,14 @@
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I202" s="36"/>
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
       <c r="L202" s="5"/>
     </row>
-    <row r="203" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A203" s="5"/>
       <c r="B203" s="15" t="s">
         <v>48</v>
@@ -9576,7 +9640,7 @@
       <c r="K203" s="12"/>
       <c r="L203" s="12"/>
     </row>
-    <row r="204" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A204" s="5"/>
       <c r="B204" s="15" t="s">
         <v>48</v>
@@ -9598,7 +9662,7 @@
       <c r="K204" s="12"/>
       <c r="L204" s="12"/>
     </row>
-    <row r="205" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A205" s="5"/>
       <c r="B205" s="15" t="s">
         <v>48</v>
@@ -9620,7 +9684,7 @@
       <c r="K205" s="12"/>
       <c r="L205" s="12"/>
     </row>
-    <row r="206" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A206" s="5"/>
       <c r="B206" s="15" t="s">
         <v>48</v>
@@ -9642,7 +9706,7 @@
       <c r="K206" s="12"/>
       <c r="L206" s="12"/>
     </row>
-    <row r="207" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A207" s="5"/>
       <c r="B207" s="15" t="s">
         <v>48</v>
@@ -9664,7 +9728,7 @@
       <c r="K207" s="12"/>
       <c r="L207" s="12"/>
     </row>
-    <row r="208" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A208" s="5"/>
       <c r="B208" s="15" t="s">
         <v>48</v>
@@ -9686,7 +9750,7 @@
       <c r="K208" s="12"/>
       <c r="L208" s="12"/>
     </row>
-    <row r="209" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A209" s="5"/>
       <c r="B209" s="15" t="s">
         <v>48</v>
@@ -9708,7 +9772,7 @@
       <c r="K209" s="12"/>
       <c r="L209" s="12"/>
     </row>
-    <row r="210" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A210" s="5"/>
       <c r="B210" s="15" t="s">
         <v>48</v>
@@ -9730,7 +9794,7 @@
       <c r="K210" s="12"/>
       <c r="L210" s="12"/>
     </row>
-    <row r="211" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A211" s="5"/>
       <c r="B211" s="15" t="s">
         <v>48</v>
@@ -9752,7 +9816,7 @@
       <c r="K211" s="12"/>
       <c r="L211" s="12"/>
     </row>
-    <row r="212" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A212" s="5"/>
       <c r="B212" s="15" t="s">
         <v>48</v>
@@ -9774,7 +9838,7 @@
       <c r="K212" s="12"/>
       <c r="L212" s="12"/>
     </row>
-    <row r="213" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A213" s="5"/>
       <c r="B213" s="15" t="s">
         <v>48</v>
@@ -9796,18 +9860,18 @@
       <c r="K213" s="12"/>
       <c r="L213" s="12"/>
     </row>
-    <row r="214" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A214" s="5"/>
       <c r="B214" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>556</v>
+        <v>462</v>
       </c>
       <c r="D214" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="E214" s="55" t="s">
+        <v>463</v>
+      </c>
+      <c r="E214" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F214" s="2" t="s">
@@ -9815,27 +9879,27 @@
       </c>
       <c r="G214" s="5"/>
       <c r="H214" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I214" s="36" t="s">
-        <v>558</v>
+        <v>62</v>
       </c>
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
       <c r="L214" s="5"/>
     </row>
-    <row r="215" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A215" s="5"/>
       <c r="B215" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>559</v>
+        <v>504</v>
       </c>
       <c r="D215" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="E215" s="55" t="s">
+        <v>505</v>
+      </c>
+      <c r="E215" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F215" s="2" t="s">
@@ -9846,24 +9910,24 @@
         <v>31</v>
       </c>
       <c r="I215" s="36" t="s">
-        <v>558</v>
+        <v>62</v>
       </c>
       <c r="J215" s="5"/>
       <c r="K215" s="5"/>
       <c r="L215" s="5"/>
     </row>
-    <row r="216" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A216" s="5"/>
       <c r="B216" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>561</v>
+        <v>506</v>
       </c>
       <c r="D216" s="24" t="s">
-        <v>562</v>
-      </c>
-      <c r="E216" s="55" t="s">
+        <v>507</v>
+      </c>
+      <c r="E216" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F216" s="2" t="s">
@@ -9874,25 +9938,25 @@
         <v>31</v>
       </c>
       <c r="I216" s="36" t="s">
-        <v>563</v>
+        <v>62</v>
       </c>
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
       <c r="L216" s="5"/>
     </row>
-    <row r="217" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A217" s="5"/>
       <c r="B217" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>564</v>
+        <v>508</v>
       </c>
       <c r="D217" s="24" t="s">
-        <v>565</v>
-      </c>
-      <c r="E217" s="55" t="s">
-        <v>15</v>
+        <v>509</v>
+      </c>
+      <c r="E217" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>47</v>
@@ -9901,14 +9965,12 @@
       <c r="H217" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I217" s="36" t="s">
-        <v>563</v>
-      </c>
+      <c r="I217" s="36"/>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
       <c r="L217" s="5"/>
     </row>
-    <row r="218" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A218" s="5"/>
       <c r="B218" s="15" t="s">
         <v>48</v>
@@ -9930,18 +9992,18 @@
       <c r="K218" s="12"/>
       <c r="L218" s="12"/>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="5"/>
       <c r="B219" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>568</v>
+        <v>512</v>
       </c>
       <c r="D219" s="24" t="s">
-        <v>569</v>
-      </c>
-      <c r="E219" s="55" t="s">
+        <v>513</v>
+      </c>
+      <c r="E219" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F219" s="2" t="s">
@@ -9949,14 +10011,14 @@
       </c>
       <c r="G219" s="5"/>
       <c r="H219" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I219" s="36"/>
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
       <c r="L219" s="5"/>
     </row>
-    <row r="220" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A220" s="5"/>
       <c r="B220" s="15" t="s">
         <v>48</v>
@@ -9978,7 +10040,7 @@
       <c r="K220" s="12"/>
       <c r="L220" s="12"/>
     </row>
-    <row r="221" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A221" s="5"/>
       <c r="B221" s="15" t="s">
         <v>48</v>
@@ -10000,7 +10062,7 @@
       <c r="K221" s="12"/>
       <c r="L221" s="12"/>
     </row>
-    <row r="222" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A222" s="5"/>
       <c r="B222" s="15" t="s">
         <v>48</v>
@@ -10022,18 +10084,18 @@
       <c r="K222" s="12"/>
       <c r="L222" s="12"/>
     </row>
-    <row r="223" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A223" s="5"/>
       <c r="B223" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="D223" s="24" t="s">
-        <v>577</v>
-      </c>
-      <c r="E223" s="55" t="s">
+        <v>515</v>
+      </c>
+      <c r="E223" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F223" s="2" t="s">
@@ -10041,27 +10103,25 @@
       </c>
       <c r="G223" s="5"/>
       <c r="H223" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I223" s="36" t="s">
-        <v>563</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I223" s="36"/>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
       <c r="L223" s="5"/>
     </row>
-    <row r="224" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A224" s="5"/>
       <c r="B224" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>578</v>
+        <v>532</v>
       </c>
       <c r="D224" s="24" t="s">
-        <v>579</v>
-      </c>
-      <c r="E224" s="55" t="s">
+        <v>533</v>
+      </c>
+      <c r="E224" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F224" s="2" t="s">
@@ -10069,16 +10129,14 @@
       </c>
       <c r="G224" s="5"/>
       <c r="H224" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I224" s="36" t="s">
-        <v>563</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I224" s="36"/>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
       <c r="L224" s="5"/>
     </row>
-    <row r="225" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A225" s="5"/>
       <c r="B225" s="15" t="s">
         <v>48</v>
@@ -10100,7 +10158,7 @@
       <c r="K225" s="12"/>
       <c r="L225" s="12"/>
     </row>
-    <row r="226" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A226" s="5"/>
       <c r="B226" s="15" t="s">
         <v>48</v>
@@ -10122,7 +10180,7 @@
       <c r="K226" s="12"/>
       <c r="L226" s="12"/>
     </row>
-    <row r="227" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A227" s="5"/>
       <c r="B227" s="15" t="s">
         <v>48</v>
@@ -10144,7 +10202,7 @@
       <c r="K227" s="12"/>
       <c r="L227" s="12"/>
     </row>
-    <row r="228" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A228" s="5"/>
       <c r="B228" s="15" t="s">
         <v>48</v>
@@ -10166,71 +10224,63 @@
       <c r="K228" s="12"/>
       <c r="L228" s="12"/>
     </row>
-    <row r="229" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A229" s="5"/>
       <c r="B229" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>588</v>
-      </c>
-      <c r="D229" s="27" t="s">
-        <v>589</v>
-      </c>
-      <c r="E229" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D229" s="24" t="s">
+        <v>557</v>
+      </c>
+      <c r="E229" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F229" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G229" s="6"/>
+      <c r="F229" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G229" s="5"/>
       <c r="H229" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I229" s="37"/>
-      <c r="J229" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K229" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="L229" s="6" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I229" s="36" t="s">
+        <v>558</v>
+      </c>
+      <c r="J229" s="5"/>
+      <c r="K229" s="5"/>
+      <c r="L229" s="5"/>
+    </row>
+    <row r="230" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A230" s="5"/>
       <c r="B230" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C230" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="D230" s="27" t="s">
-        <v>593</v>
-      </c>
-      <c r="E230" s="6" t="s">
+      <c r="C230" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D230" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="E230" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F230" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G230" s="6"/>
+      <c r="F230" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G230" s="5"/>
       <c r="H230" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I230" s="37"/>
-      <c r="J230" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="K230" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="L230" s="6" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="I230" s="36" t="s">
+        <v>558</v>
+      </c>
+      <c r="J230" s="5"/>
+      <c r="K230" s="5"/>
+      <c r="L230" s="5"/>
+    </row>
+    <row r="231" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A231" s="5"/>
       <c r="B231" s="15" t="s">
         <v>48</v>
@@ -10252,7 +10302,7 @@
       <c r="K231" s="12"/>
       <c r="L231" s="12"/>
     </row>
-    <row r="232" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A232" s="5"/>
       <c r="B232" s="15" t="s">
         <v>48</v>
@@ -10274,7 +10324,7 @@
       <c r="K232" s="12"/>
       <c r="L232" s="12"/>
     </row>
-    <row r="233" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A233" s="5"/>
       <c r="B233" s="15" t="s">
         <v>48</v>
@@ -10296,7 +10346,7 @@
       <c r="K233" s="12"/>
       <c r="L233" s="12"/>
     </row>
-    <row r="234" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A234" s="5"/>
       <c r="B234" s="15" t="s">
         <v>48</v>
@@ -10318,7 +10368,7 @@
       <c r="K234" s="12"/>
       <c r="L234" s="12"/>
     </row>
-    <row r="235" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A235" s="5"/>
       <c r="B235" s="15" t="s">
         <v>48</v>
@@ -10340,7 +10390,7 @@
       <c r="K235" s="12"/>
       <c r="L235" s="12"/>
     </row>
-    <row r="236" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A236" s="5"/>
       <c r="B236" s="15" t="s">
         <v>48</v>
@@ -10362,97 +10412,89 @@
       <c r="K236" s="12"/>
       <c r="L236" s="12"/>
     </row>
-    <row r="237" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A237" s="5"/>
       <c r="B237" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C237" s="29" t="s">
-        <v>607</v>
-      </c>
-      <c r="D237" s="30" t="s">
-        <v>608</v>
-      </c>
-      <c r="E237" s="56" t="s">
+      <c r="C237" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D237" s="24" t="s">
+        <v>562</v>
+      </c>
+      <c r="E237" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F237" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G237" s="42"/>
+      <c r="F237" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G237" s="5"/>
       <c r="H237" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I237" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="J237" s="42"/>
-      <c r="K237" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="L237" s="42"/>
-    </row>
-    <row r="238" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+      <c r="J237" s="5"/>
+      <c r="K237" s="5"/>
+      <c r="L237" s="5"/>
+    </row>
+    <row r="238" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A238" s="5"/>
       <c r="B238" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C238" s="29" t="s">
-        <v>611</v>
-      </c>
-      <c r="D238" s="30" t="s">
-        <v>612</v>
-      </c>
-      <c r="E238" s="56" t="s">
+      <c r="C238" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D238" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="E238" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F238" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G238" s="42"/>
+      <c r="F238" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G238" s="5"/>
       <c r="H238" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I238" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="J238" s="42"/>
-      <c r="K238" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="L238" s="42"/>
-    </row>
-    <row r="239" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+      <c r="J238" s="5"/>
+      <c r="K238" s="5"/>
+      <c r="L238" s="5"/>
+    </row>
+    <row r="239" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A239" s="5"/>
       <c r="B239" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C239" s="29" t="s">
-        <v>614</v>
-      </c>
-      <c r="D239" s="30" t="s">
-        <v>615</v>
-      </c>
-      <c r="E239" s="56" t="s">
+      <c r="C239" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D239" s="24" t="s">
+        <v>569</v>
+      </c>
+      <c r="E239" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F239" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G239" s="42"/>
+      <c r="F239" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G239" s="5"/>
       <c r="H239" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I239" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="J239" s="42"/>
-      <c r="K239" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="L239" s="42"/>
-    </row>
-    <row r="240" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="I239" s="36"/>
+      <c r="J239" s="5"/>
+      <c r="K239" s="5"/>
+      <c r="L239" s="5"/>
+    </row>
+    <row r="240" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A240" s="5"/>
       <c r="B240" s="15" t="s">
         <v>48</v>
@@ -10474,7 +10516,7 @@
       <c r="K240" s="12"/>
       <c r="L240" s="12"/>
     </row>
-    <row r="241" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A241" s="5"/>
       <c r="B241" s="15" t="s">
         <v>48</v>
@@ -10496,7 +10538,7 @@
       <c r="K241" s="12"/>
       <c r="L241" s="12"/>
     </row>
-    <row r="242" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A242" s="5"/>
       <c r="B242" s="15" t="s">
         <v>48</v>
@@ -10518,7 +10560,7 @@
       <c r="K242" s="12"/>
       <c r="L242" s="12"/>
     </row>
-    <row r="243" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A243" s="5"/>
       <c r="B243" s="15" t="s">
         <v>48</v>
@@ -10540,7 +10582,7 @@
       <c r="K243" s="12"/>
       <c r="L243" s="12"/>
     </row>
-    <row r="244" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A244" s="5"/>
       <c r="B244" s="15" t="s">
         <v>48</v>
@@ -10562,7 +10604,7 @@
       <c r="K244" s="12"/>
       <c r="L244" s="12"/>
     </row>
-    <row r="245" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A245" s="5"/>
       <c r="B245" s="15" t="s">
         <v>48</v>
@@ -10584,7 +10626,7 @@
       <c r="K245" s="12"/>
       <c r="L245" s="12"/>
     </row>
-    <row r="246" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A246" s="5"/>
       <c r="B246" s="15" t="s">
         <v>48</v>
@@ -10606,7 +10648,7 @@
       <c r="K246" s="12"/>
       <c r="L246" s="12"/>
     </row>
-    <row r="247" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A247" s="5"/>
       <c r="B247" s="15" t="s">
         <v>48</v>
@@ -10628,7 +10670,7 @@
       <c r="K247" s="12"/>
       <c r="L247" s="12"/>
     </row>
-    <row r="248" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A248" s="5"/>
       <c r="B248" s="15" t="s">
         <v>48</v>
@@ -10650,7 +10692,7 @@
       <c r="K248" s="12"/>
       <c r="L248" s="12"/>
     </row>
-    <row r="249" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A249" s="5"/>
       <c r="B249" s="15" t="s">
         <v>48</v>
@@ -10672,7 +10714,7 @@
       <c r="K249" s="12"/>
       <c r="L249" s="12"/>
     </row>
-    <row r="250" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A250" s="5"/>
       <c r="B250" s="15" t="s">
         <v>48</v>
@@ -10694,7 +10736,7 @@
       <c r="K250" s="12"/>
       <c r="L250" s="12"/>
     </row>
-    <row r="251" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A251" s="5"/>
       <c r="B251" s="15" t="s">
         <v>48</v>
@@ -10716,7 +10758,7 @@
       <c r="K251" s="12"/>
       <c r="L251" s="12"/>
     </row>
-    <row r="252" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A252" s="5"/>
       <c r="B252" s="15" t="s">
         <v>48</v>
@@ -10738,7 +10780,7 @@
       <c r="K252" s="12"/>
       <c r="L252" s="12"/>
     </row>
-    <row r="253" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A253" s="5"/>
       <c r="B253" s="15" t="s">
         <v>48</v>
@@ -10760,7 +10802,7 @@
       <c r="K253" s="12"/>
       <c r="L253" s="12"/>
     </row>
-    <row r="254" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A254" s="5"/>
       <c r="B254" s="15" t="s">
         <v>48</v>
@@ -10782,7 +10824,7 @@
       <c r="K254" s="12"/>
       <c r="L254" s="12"/>
     </row>
-    <row r="255" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A255" s="5"/>
       <c r="B255" s="15" t="s">
         <v>48</v>
@@ -10804,7 +10846,7 @@
       <c r="K255" s="12"/>
       <c r="L255" s="12"/>
     </row>
-    <row r="256" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A256" s="5"/>
       <c r="B256" s="15" t="s">
         <v>48</v>
@@ -10826,7 +10868,7 @@
       <c r="K256" s="12"/>
       <c r="L256" s="12"/>
     </row>
-    <row r="257" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A257" s="5"/>
       <c r="B257" s="15" t="s">
         <v>48</v>
@@ -10848,7 +10890,7 @@
       <c r="K257" s="12"/>
       <c r="L257" s="12"/>
     </row>
-    <row r="258" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A258" s="5"/>
       <c r="B258" s="15" t="s">
         <v>48</v>
@@ -10870,7 +10912,7 @@
       <c r="K258" s="12"/>
       <c r="L258" s="12"/>
     </row>
-    <row r="259" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A259" s="5"/>
       <c r="B259" s="15" t="s">
         <v>48</v>
@@ -10892,7 +10934,7 @@
       <c r="K259" s="12"/>
       <c r="L259" s="12"/>
     </row>
-    <row r="260" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A260" s="5"/>
       <c r="B260" s="15" t="s">
         <v>48</v>
@@ -10914,7 +10956,7 @@
       <c r="K260" s="12"/>
       <c r="L260" s="12"/>
     </row>
-    <row r="261" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A261" s="5"/>
       <c r="B261" s="15" t="s">
         <v>48</v>
@@ -10936,7 +10978,7 @@
       <c r="K261" s="12"/>
       <c r="L261" s="12"/>
     </row>
-    <row r="262" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A262" s="5"/>
       <c r="B262" s="15" t="s">
         <v>48</v>
@@ -10958,7 +11000,7 @@
       <c r="K262" s="12"/>
       <c r="L262" s="12"/>
     </row>
-    <row r="263" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A263" s="5"/>
       <c r="B263" s="15" t="s">
         <v>48</v>
@@ -10980,7 +11022,7 @@
       <c r="K263" s="12"/>
       <c r="L263" s="12"/>
     </row>
-    <row r="264" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A264" s="5"/>
       <c r="B264" s="15" t="s">
         <v>48</v>
@@ -11002,7 +11044,7 @@
       <c r="K264" s="12"/>
       <c r="L264" s="12"/>
     </row>
-    <row r="265" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A265" s="5"/>
       <c r="B265" s="15" t="s">
         <v>48</v>
@@ -11024,7 +11066,7 @@
       <c r="K265" s="12"/>
       <c r="L265" s="12"/>
     </row>
-    <row r="266" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A266" s="5"/>
       <c r="B266" s="15" t="s">
         <v>48</v>
@@ -11046,7 +11088,7 @@
       <c r="K266" s="12"/>
       <c r="L266" s="12"/>
     </row>
-    <row r="267" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A267" s="5"/>
       <c r="B267" s="15" t="s">
         <v>48</v>
@@ -11068,7 +11110,7 @@
       <c r="K267" s="12"/>
       <c r="L267" s="12"/>
     </row>
-    <row r="268" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A268" s="5"/>
       <c r="B268" s="15" t="s">
         <v>48</v>
@@ -11090,7 +11132,7 @@
       <c r="K268" s="12"/>
       <c r="L268" s="12"/>
     </row>
-    <row r="269" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A269" s="5"/>
       <c r="B269" s="15" t="s">
         <v>48</v>
@@ -11112,7 +11154,7 @@
       <c r="K269" s="12"/>
       <c r="L269" s="12"/>
     </row>
-    <row r="270" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A270" s="5"/>
       <c r="B270" s="15" t="s">
         <v>48</v>
@@ -11134,7 +11176,7 @@
       <c r="K270" s="12"/>
       <c r="L270" s="12"/>
     </row>
-    <row r="271" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A271" s="5"/>
       <c r="B271" s="15" t="s">
         <v>48</v>
@@ -11156,7 +11198,7 @@
       <c r="K271" s="12"/>
       <c r="L271" s="12"/>
     </row>
-    <row r="272" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A272" s="5"/>
       <c r="B272" s="15" t="s">
         <v>48</v>
@@ -11178,7 +11220,7 @@
       <c r="K272" s="12"/>
       <c r="L272" s="12"/>
     </row>
-    <row r="273" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A273" s="5"/>
       <c r="B273" s="15" t="s">
         <v>48</v>
@@ -11200,7 +11242,7 @@
       <c r="K273" s="12"/>
       <c r="L273" s="12"/>
     </row>
-    <row r="274" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A274" s="5"/>
       <c r="B274" s="15" t="s">
         <v>48</v>
@@ -11222,7 +11264,7 @@
       <c r="K274" s="12"/>
       <c r="L274" s="12"/>
     </row>
-    <row r="275" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A275" s="5"/>
       <c r="B275" s="15" t="s">
         <v>48</v>
@@ -11244,7 +11286,7 @@
       <c r="K275" s="12"/>
       <c r="L275" s="12"/>
     </row>
-    <row r="276" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A276" s="5"/>
       <c r="B276" s="15" t="s">
         <v>48</v>
@@ -11266,7 +11308,7 @@
       <c r="K276" s="12"/>
       <c r="L276" s="12"/>
     </row>
-    <row r="277" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A277" s="5"/>
       <c r="B277" s="15" t="s">
         <v>48</v>
@@ -11288,7 +11330,7 @@
       <c r="K277" s="12"/>
       <c r="L277" s="12"/>
     </row>
-    <row r="278" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A278" s="5"/>
       <c r="B278" s="15" t="s">
         <v>48</v>
@@ -11310,7 +11352,7 @@
       <c r="K278" s="12"/>
       <c r="L278" s="12"/>
     </row>
-    <row r="279" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A279" s="5"/>
       <c r="B279" s="15" t="s">
         <v>48</v>
@@ -11332,7 +11374,7 @@
       <c r="K279" s="12"/>
       <c r="L279" s="12"/>
     </row>
-    <row r="280" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A280" s="5"/>
       <c r="B280" s="15" t="s">
         <v>48</v>
@@ -11354,7 +11396,7 @@
       <c r="K280" s="12"/>
       <c r="L280" s="12"/>
     </row>
-    <row r="281" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A281" s="5"/>
       <c r="B281" s="15" t="s">
         <v>48</v>
@@ -11376,7 +11418,7 @@
       <c r="K281" s="12"/>
       <c r="L281" s="12"/>
     </row>
-    <row r="282" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A282" s="5"/>
       <c r="B282" s="15" t="s">
         <v>48</v>
@@ -11398,7 +11440,7 @@
       <c r="K282" s="12"/>
       <c r="L282" s="12"/>
     </row>
-    <row r="283" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A283" s="5"/>
       <c r="B283" s="15" t="s">
         <v>48</v>
@@ -11420,7 +11462,7 @@
       <c r="K283" s="12"/>
       <c r="L283" s="12"/>
     </row>
-    <row r="284" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A284" s="5"/>
       <c r="B284" s="15" t="s">
         <v>48</v>
@@ -11442,7 +11484,7 @@
       <c r="K284" s="12"/>
       <c r="L284" s="12"/>
     </row>
-    <row r="285" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A285" s="5"/>
       <c r="B285" s="15" t="s">
         <v>48</v>
@@ -11464,7 +11506,7 @@
       <c r="K285" s="12"/>
       <c r="L285" s="12"/>
     </row>
-    <row r="286" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A286" s="5"/>
       <c r="B286" s="15" t="s">
         <v>48</v>
@@ -11486,7 +11528,7 @@
       <c r="K286" s="12"/>
       <c r="L286" s="12"/>
     </row>
-    <row r="287" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A287" s="5"/>
       <c r="B287" s="15" t="s">
         <v>48</v>
@@ -11508,7 +11550,7 @@
       <c r="K287" s="12"/>
       <c r="L287" s="12"/>
     </row>
-    <row r="288" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A288" s="5"/>
       <c r="B288" s="15" t="s">
         <v>48</v>
@@ -11530,7 +11572,7 @@
       <c r="K288" s="12"/>
       <c r="L288" s="12"/>
     </row>
-    <row r="289" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A289" s="5"/>
       <c r="B289" s="15" t="s">
         <v>48</v>
@@ -11552,7 +11594,7 @@
       <c r="K289" s="12"/>
       <c r="L289" s="12"/>
     </row>
-    <row r="290" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A290" s="5"/>
       <c r="B290" s="15" t="s">
         <v>48</v>
@@ -11574,7 +11616,7 @@
       <c r="K290" s="12"/>
       <c r="L290" s="12"/>
     </row>
-    <row r="291" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A291" s="5"/>
       <c r="B291" s="15" t="s">
         <v>48</v>
@@ -11596,7 +11638,7 @@
       <c r="K291" s="12"/>
       <c r="L291" s="12"/>
     </row>
-    <row r="292" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A292" s="5"/>
       <c r="B292" s="15" t="s">
         <v>48</v>
@@ -11618,7 +11660,7 @@
       <c r="K292" s="12"/>
       <c r="L292" s="12"/>
     </row>
-    <row r="293" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A293" s="5"/>
       <c r="B293" s="15" t="s">
         <v>48</v>
@@ -11640,7 +11682,7 @@
       <c r="K293" s="12"/>
       <c r="L293" s="12"/>
     </row>
-    <row r="294" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A294" s="5"/>
       <c r="B294" s="15" t="s">
         <v>48</v>
@@ -11662,7 +11704,7 @@
       <c r="K294" s="12"/>
       <c r="L294" s="12"/>
     </row>
-    <row r="295" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A295" s="5"/>
       <c r="B295" s="15" t="s">
         <v>48</v>
@@ -11684,7 +11726,7 @@
       <c r="K295" s="12"/>
       <c r="L295" s="12"/>
     </row>
-    <row r="296" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A296" s="5"/>
       <c r="B296" s="15" t="s">
         <v>48</v>
@@ -11706,7 +11748,7 @@
       <c r="K296" s="12"/>
       <c r="L296" s="12"/>
     </row>
-    <row r="297" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A297" s="5"/>
       <c r="B297" s="15" t="s">
         <v>48</v>
@@ -11728,7 +11770,7 @@
       <c r="K297" s="12"/>
       <c r="L297" s="12"/>
     </row>
-    <row r="298" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A298" s="5"/>
       <c r="B298" s="15" t="s">
         <v>48</v>
@@ -11750,7 +11792,7 @@
       <c r="K298" s="12"/>
       <c r="L298" s="12"/>
     </row>
-    <row r="299" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A299" s="5"/>
       <c r="B299" s="15" t="s">
         <v>48</v>
@@ -11772,7 +11814,7 @@
       <c r="K299" s="12"/>
       <c r="L299" s="12"/>
     </row>
-    <row r="300" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A300" s="5"/>
       <c r="B300" s="15" t="s">
         <v>48</v>
@@ -11794,7 +11836,7 @@
       <c r="K300" s="12"/>
       <c r="L300" s="12"/>
     </row>
-    <row r="301" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A301" s="5"/>
       <c r="B301" s="15" t="s">
         <v>48</v>
@@ -11816,7 +11858,7 @@
       <c r="K301" s="12"/>
       <c r="L301" s="12"/>
     </row>
-    <row r="302" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A302" s="5"/>
       <c r="B302" s="15" t="s">
         <v>48</v>
@@ -11838,7 +11880,7 @@
       <c r="K302" s="12"/>
       <c r="L302" s="12"/>
     </row>
-    <row r="303" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A303" s="5"/>
       <c r="B303" s="15" t="s">
         <v>48</v>
@@ -11860,7 +11902,7 @@
       <c r="K303" s="12"/>
       <c r="L303" s="12"/>
     </row>
-    <row r="304" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A304" s="5"/>
       <c r="B304" s="15" t="s">
         <v>48</v>
@@ -11882,7 +11924,7 @@
       <c r="K304" s="12"/>
       <c r="L304" s="12"/>
     </row>
-    <row r="305" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A305" s="5"/>
       <c r="B305" s="15" t="s">
         <v>48</v>
@@ -11904,7 +11946,7 @@
       <c r="K305" s="12"/>
       <c r="L305" s="12"/>
     </row>
-    <row r="306" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A306" s="5"/>
       <c r="B306" s="15" t="s">
         <v>48</v>
@@ -11926,7 +11968,7 @@
       <c r="K306" s="12"/>
       <c r="L306" s="12"/>
     </row>
-    <row r="307" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A307" s="5"/>
       <c r="B307" s="15" t="s">
         <v>48</v>
@@ -11948,7 +11990,7 @@
       <c r="K307" s="12"/>
       <c r="L307" s="12"/>
     </row>
-    <row r="308" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A308" s="5"/>
       <c r="B308" s="15" t="s">
         <v>48</v>
@@ -11970,7 +12012,7 @@
       <c r="K308" s="12"/>
       <c r="L308" s="12"/>
     </row>
-    <row r="309" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A309" s="5"/>
       <c r="B309" s="15" t="s">
         <v>48</v>
@@ -11992,7 +12034,7 @@
       <c r="K309" s="12"/>
       <c r="L309" s="12"/>
     </row>
-    <row r="310" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A310" s="5"/>
       <c r="B310" s="15" t="s">
         <v>48</v>
@@ -12014,7 +12056,7 @@
       <c r="K310" s="12"/>
       <c r="L310" s="12"/>
     </row>
-    <row r="311" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A311" s="5"/>
       <c r="B311" s="15" t="s">
         <v>48</v>
@@ -12036,7 +12078,7 @@
       <c r="K311" s="12"/>
       <c r="L311" s="12"/>
     </row>
-    <row r="312" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A312" s="5"/>
       <c r="B312" s="15" t="s">
         <v>48</v>
@@ -12058,7 +12100,7 @@
       <c r="K312" s="12"/>
       <c r="L312" s="12"/>
     </row>
-    <row r="313" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A313" s="5"/>
       <c r="B313" s="15" t="s">
         <v>48</v>
@@ -12080,7 +12122,7 @@
       <c r="K313" s="12"/>
       <c r="L313" s="12"/>
     </row>
-    <row r="314" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A314" s="5"/>
       <c r="B314" s="15" t="s">
         <v>48</v>
@@ -12102,7 +12144,7 @@
       <c r="K314" s="12"/>
       <c r="L314" s="12"/>
     </row>
-    <row r="315" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A315" s="5"/>
       <c r="B315" s="15" t="s">
         <v>48</v>
@@ -12124,7 +12166,7 @@
       <c r="K315" s="12"/>
       <c r="L315" s="12"/>
     </row>
-    <row r="316" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A316" s="5"/>
       <c r="B316" s="15" t="s">
         <v>48</v>
@@ -12146,7 +12188,7 @@
       <c r="K316" s="12"/>
       <c r="L316" s="12"/>
     </row>
-    <row r="317" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A317" s="5"/>
       <c r="B317" s="15" t="s">
         <v>48</v>
@@ -12168,7 +12210,7 @@
       <c r="K317" s="12"/>
       <c r="L317" s="12"/>
     </row>
-    <row r="318" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A318" s="5"/>
       <c r="B318" s="15" t="s">
         <v>48</v>
@@ -12190,7 +12232,7 @@
       <c r="K318" s="12"/>
       <c r="L318" s="12"/>
     </row>
-    <row r="319" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A319" s="5"/>
       <c r="B319" s="15" t="s">
         <v>48</v>
@@ -12212,7 +12254,7 @@
       <c r="K319" s="12"/>
       <c r="L319" s="12"/>
     </row>
-    <row r="320" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A320" s="5"/>
       <c r="B320" s="15" t="s">
         <v>48</v>
@@ -12234,7 +12276,7 @@
       <c r="K320" s="12"/>
       <c r="L320" s="12"/>
     </row>
-    <row r="321" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A321" s="5"/>
       <c r="B321" s="15" t="s">
         <v>48</v>
@@ -12256,7 +12298,7 @@
       <c r="K321" s="12"/>
       <c r="L321" s="12"/>
     </row>
-    <row r="322" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A322" s="5"/>
       <c r="B322" s="15" t="s">
         <v>48</v>
@@ -12278,7 +12320,7 @@
       <c r="K322" s="12"/>
       <c r="L322" s="12"/>
     </row>
-    <row r="323" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A323" s="5"/>
       <c r="B323" s="15" t="s">
         <v>48</v>
@@ -12300,7 +12342,7 @@
       <c r="K323" s="12"/>
       <c r="L323" s="12"/>
     </row>
-    <row r="324" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A324" s="5"/>
       <c r="B324" s="15" t="s">
         <v>48</v>
@@ -12322,7 +12364,7 @@
       <c r="K324" s="12"/>
       <c r="L324" s="12"/>
     </row>
-    <row r="325" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A325" s="5"/>
       <c r="B325" s="15" t="s">
         <v>48</v>
@@ -12344,7 +12386,7 @@
       <c r="K325" s="12"/>
       <c r="L325" s="12"/>
     </row>
-    <row r="326" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A326" s="5"/>
       <c r="B326" s="15" t="s">
         <v>48</v>
@@ -12366,7 +12408,7 @@
       <c r="K326" s="12"/>
       <c r="L326" s="12"/>
     </row>
-    <row r="327" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A327" s="5"/>
       <c r="B327" s="15" t="s">
         <v>48</v>
@@ -12388,7 +12430,7 @@
       <c r="K327" s="12"/>
       <c r="L327" s="12"/>
     </row>
-    <row r="328" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A328" s="5"/>
       <c r="B328" s="15" t="s">
         <v>48</v>
@@ -12410,18 +12452,18 @@
       <c r="K328" s="12"/>
       <c r="L328" s="12"/>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="5"/>
       <c r="B329" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>794</v>
+        <v>576</v>
       </c>
       <c r="D329" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="E329" s="55" t="s">
+        <v>577</v>
+      </c>
+      <c r="E329" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F329" s="2" t="s">
@@ -12429,27 +12471,27 @@
       </c>
       <c r="G329" s="5"/>
       <c r="H329" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I329" s="37" t="s">
-        <v>264</v>
+        <v>23</v>
+      </c>
+      <c r="I329" s="36" t="s">
+        <v>563</v>
       </c>
       <c r="J329" s="5"/>
       <c r="K329" s="5"/>
       <c r="L329" s="5"/>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="5"/>
       <c r="B330" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>795</v>
+        <v>578</v>
       </c>
       <c r="D330" s="24" t="s">
-        <v>796</v>
-      </c>
-      <c r="E330" s="55" t="s">
+        <v>579</v>
+      </c>
+      <c r="E330" s="53" t="s">
         <v>15</v>
       </c>
       <c r="F330" s="2" t="s">
@@ -12457,66 +12499,78 @@
       </c>
       <c r="G330" s="5"/>
       <c r="H330" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I330" s="36"/>
+        <v>23</v>
+      </c>
+      <c r="I330" s="36" t="s">
+        <v>563</v>
+      </c>
       <c r="J330" s="5"/>
       <c r="K330" s="5"/>
       <c r="L330" s="5"/>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="5"/>
       <c r="B331" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C331" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D331" s="24" t="s">
-        <v>798</v>
-      </c>
-      <c r="E331" s="55" t="s">
+      <c r="C331" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="D331" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="E331" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F331" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G331" s="5"/>
+      <c r="F331" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G331" s="6"/>
       <c r="H331" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I331" s="36"/>
-      <c r="J331" s="5"/>
-      <c r="K331" s="5"/>
-      <c r="L331" s="5"/>
-    </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="I331" s="37"/>
+      <c r="J331" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="K331" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="L331" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="5"/>
       <c r="B332" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C332" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="D332" s="26" t="s">
-        <v>800</v>
-      </c>
-      <c r="E332" s="10" t="s">
+      <c r="C332" s="29" t="s">
+        <v>607</v>
+      </c>
+      <c r="D332" s="30" t="s">
+        <v>608</v>
+      </c>
+      <c r="E332" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F332" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G332" s="5"/>
+      <c r="F332" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G332" s="42"/>
       <c r="H332" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I332" s="36"/>
-      <c r="J332" s="5"/>
-      <c r="K332" s="5"/>
-      <c r="L332" s="5"/>
-    </row>
-    <row r="333" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I332" s="36" t="s">
+        <v>609</v>
+      </c>
+      <c r="J332" s="42"/>
+      <c r="K332" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="L332" s="42"/>
+    </row>
+    <row r="333" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
       <c r="B333" s="5" t="s">
         <v>21</v>
@@ -12548,7 +12602,7 @@
       </c>
       <c r="L333" s="12"/>
     </row>
-    <row r="334" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
       <c r="B334" s="5" t="s">
         <v>21</v>
@@ -12582,33 +12636,37 @@
         <v>807</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
       <c r="B335" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C335" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="D335" s="26" t="s">
-        <v>809</v>
-      </c>
-      <c r="E335" s="10" t="s">
+      <c r="C335" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="D335" s="30" t="s">
+        <v>612</v>
+      </c>
+      <c r="E335" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F335" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G335" s="5"/>
+      <c r="F335" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G335" s="42"/>
       <c r="H335" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I335" s="36"/>
-      <c r="J335" s="5"/>
-      <c r="K335" s="5"/>
-      <c r="L335" s="5"/>
-    </row>
-    <row r="336" spans="1:12" customFormat="1" ht="120" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I335" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="J335" s="42"/>
+      <c r="K335" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="L335" s="42"/>
+    </row>
+    <row r="336" spans="1:12" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A336" s="5"/>
       <c r="B336" s="5" t="s">
         <v>21</v>
@@ -12640,7 +12698,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="337" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A337" s="5"/>
       <c r="B337" s="15" t="s">
         <v>48</v>
@@ -12662,7 +12720,7 @@
       <c r="K337" s="12"/>
       <c r="L337" s="12"/>
     </row>
-    <row r="338" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A338" s="5"/>
       <c r="B338" s="15" t="s">
         <v>48</v>
@@ -12684,7 +12742,7 @@
       <c r="K338" s="12"/>
       <c r="L338" s="12"/>
     </row>
-    <row r="339" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A339" s="5"/>
       <c r="B339" s="15" t="s">
         <v>48</v>
@@ -12706,7 +12764,7 @@
       <c r="K339" s="12"/>
       <c r="L339" s="12"/>
     </row>
-    <row r="340" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A340" s="5"/>
       <c r="B340" s="15" t="s">
         <v>48</v>
@@ -12728,7 +12786,7 @@
       <c r="K340" s="12"/>
       <c r="L340" s="12"/>
     </row>
-    <row r="341" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A341" s="5"/>
       <c r="B341" s="15" t="s">
         <v>48</v>
@@ -12750,7 +12808,7 @@
       <c r="K341" s="12"/>
       <c r="L341" s="12"/>
     </row>
-    <row r="342" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A342" s="5"/>
       <c r="B342" s="15" t="s">
         <v>48</v>
@@ -12772,7 +12830,7 @@
       <c r="K342" s="12"/>
       <c r="L342" s="12"/>
     </row>
-    <row r="343" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A343" s="5"/>
       <c r="B343" s="15" t="s">
         <v>48</v>
@@ -12794,7 +12852,7 @@
       <c r="K343" s="12"/>
       <c r="L343" s="12"/>
     </row>
-    <row r="344" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A344" s="5"/>
       <c r="B344" s="15" t="s">
         <v>48</v>
@@ -12816,7 +12874,7 @@
       <c r="K344" s="12"/>
       <c r="L344" s="12"/>
     </row>
-    <row r="345" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A345" s="5"/>
       <c r="B345" s="15" t="s">
         <v>48</v>
@@ -12838,7 +12896,7 @@
       <c r="K345" s="12"/>
       <c r="L345" s="12"/>
     </row>
-    <row r="346" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A346" s="5"/>
       <c r="B346" s="15" t="s">
         <v>48</v>
@@ -12860,7 +12918,7 @@
       <c r="K346" s="12"/>
       <c r="L346" s="12"/>
     </row>
-    <row r="347" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A347" s="5"/>
       <c r="B347" s="15" t="s">
         <v>48</v>
@@ -12882,7 +12940,7 @@
       <c r="K347" s="12"/>
       <c r="L347" s="12"/>
     </row>
-    <row r="348" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A348" s="5"/>
       <c r="B348" s="15" t="s">
         <v>48</v>
@@ -12904,95 +12962,91 @@
       <c r="K348" s="12"/>
       <c r="L348" s="12"/>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="5"/>
       <c r="B349" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C349" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="D349" s="24" t="s">
-        <v>838</v>
-      </c>
-      <c r="E349" s="55" t="s">
+      <c r="C349" s="29" t="s">
+        <v>614</v>
+      </c>
+      <c r="D349" s="30" t="s">
+        <v>615</v>
+      </c>
+      <c r="E349" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F349" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G349" s="5"/>
+      <c r="F349" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G349" s="42"/>
       <c r="H349" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I349" s="36" t="s">
-        <v>839</v>
-      </c>
-      <c r="J349" s="5"/>
-      <c r="K349" s="5"/>
-      <c r="L349" s="5"/>
-    </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+      <c r="J349" s="42"/>
+      <c r="K349" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="L349" s="42"/>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="5"/>
       <c r="B350" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C350" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="D350" s="26" t="s">
-        <v>841</v>
-      </c>
-      <c r="E350" s="10" t="s">
+      <c r="C350" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="D350" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="E350" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F350" s="5" t="s">
-        <v>16</v>
+      <c r="F350" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="G350" s="5"/>
       <c r="H350" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I350" s="36"/>
+      <c r="I350" s="37" t="s">
+        <v>264</v>
+      </c>
       <c r="J350" s="5"/>
-      <c r="K350" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="L350" s="5" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K350" s="5"/>
+      <c r="L350" s="5"/>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="5"/>
       <c r="B351" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C351" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="D351" s="26" t="s">
-        <v>845</v>
-      </c>
-      <c r="E351" s="10" t="s">
+      <c r="C351" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D351" s="24" t="s">
+        <v>796</v>
+      </c>
+      <c r="E351" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F351" s="5" t="s">
-        <v>16</v>
+      <c r="F351" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="G351" s="5"/>
       <c r="H351" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I351" s="36" t="s">
-        <v>846</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="I351" s="36"/>
       <c r="J351" s="5"/>
-      <c r="K351" s="5" t="s">
-        <v>847</v>
-      </c>
+      <c r="K351" s="5"/>
       <c r="L351" s="5"/>
     </row>
-    <row r="352" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A352" s="5"/>
       <c r="B352" s="5" t="s">
         <v>21</v>
@@ -13024,65 +13078,59 @@
       </c>
       <c r="L352" s="12"/>
     </row>
-    <row r="353" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A353" s="5"/>
       <c r="B353" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C353" s="29" t="s">
-        <v>851</v>
-      </c>
-      <c r="D353" s="30" t="s">
-        <v>852</v>
-      </c>
-      <c r="E353" s="56" t="s">
+      <c r="C353" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D353" s="24" t="s">
+        <v>798</v>
+      </c>
+      <c r="E353" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F353" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G353" s="42"/>
+      <c r="F353" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G353" s="5"/>
       <c r="H353" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I353" s="36" t="s">
-        <v>853</v>
-      </c>
-      <c r="J353" s="42"/>
-      <c r="K353" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="L353" s="42"/>
-    </row>
-    <row r="354" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="I353" s="36"/>
+      <c r="J353" s="5"/>
+      <c r="K353" s="5"/>
+      <c r="L353" s="5"/>
+    </row>
+    <row r="354" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A354" s="5"/>
       <c r="B354" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C354" s="29" t="s">
-        <v>854</v>
-      </c>
-      <c r="D354" s="29" t="s">
-        <v>855</v>
-      </c>
-      <c r="E354" s="56" t="s">
+      <c r="C354" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="D354" s="26" t="s">
+        <v>800</v>
+      </c>
+      <c r="E354" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F354" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G354" s="42"/>
+      <c r="F354" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G354" s="5"/>
       <c r="H354" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I354" s="36" t="s">
-        <v>856</v>
-      </c>
-      <c r="J354" s="42"/>
-      <c r="K354" s="42"/>
-      <c r="L354" s="42"/>
-    </row>
-    <row r="355" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I354" s="36"/>
+      <c r="J354" s="5"/>
+      <c r="K354" s="5"/>
+      <c r="L354" s="5"/>
+    </row>
+    <row r="355" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A355" s="5"/>
       <c r="B355" s="15" t="s">
         <v>48</v>
@@ -13104,7 +13152,7 @@
       <c r="K355" s="12"/>
       <c r="L355" s="12"/>
     </row>
-    <row r="356" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A356" s="5"/>
       <c r="B356" s="15" t="s">
         <v>48</v>
@@ -13126,63 +13174,61 @@
       <c r="K356" s="12"/>
       <c r="L356" s="12"/>
     </row>
-    <row r="357" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A357" s="5"/>
       <c r="B357" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C357" s="29" t="s">
-        <v>861</v>
-      </c>
-      <c r="D357" s="29" t="s">
-        <v>862</v>
-      </c>
-      <c r="E357" s="56" t="s">
+      <c r="C357" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="D357" s="26" t="s">
+        <v>809</v>
+      </c>
+      <c r="E357" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F357" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G357" s="42"/>
+      <c r="F357" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G357" s="5"/>
       <c r="H357" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I357" s="36" t="s">
-        <v>856</v>
-      </c>
-      <c r="J357" s="42"/>
-      <c r="K357" s="42"/>
-      <c r="L357" s="42"/>
-    </row>
-    <row r="358" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="I357" s="36"/>
+      <c r="J357" s="5"/>
+      <c r="K357" s="5"/>
+      <c r="L357" s="5"/>
+    </row>
+    <row r="358" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A358" s="5"/>
       <c r="B358" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C358" s="29" t="s">
-        <v>863</v>
-      </c>
-      <c r="D358" s="29" t="s">
-        <v>864</v>
-      </c>
-      <c r="E358" s="56" t="s">
+      <c r="C358" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="D358" s="24" t="s">
+        <v>838</v>
+      </c>
+      <c r="E358" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F358" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G358" s="42"/>
+      <c r="F358" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G358" s="5"/>
       <c r="H358" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I358" s="36" t="s">
-        <v>856</v>
-      </c>
-      <c r="J358" s="42"/>
-      <c r="K358" s="42"/>
-      <c r="L358" s="42"/>
-    </row>
-    <row r="359" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+        <v>839</v>
+      </c>
+      <c r="J358" s="5"/>
+      <c r="K358" s="5"/>
+      <c r="L358" s="5"/>
+    </row>
+    <row r="359" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A359" s="5"/>
       <c r="B359" s="15" t="s">
         <v>48</v>
@@ -13204,7 +13250,7 @@
       <c r="K359" s="12"/>
       <c r="L359" s="12"/>
     </row>
-    <row r="360" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A360" s="5"/>
       <c r="B360" s="15" t="s">
         <v>48</v>
@@ -13226,7 +13272,7 @@
       <c r="K360" s="12"/>
       <c r="L360" s="12"/>
     </row>
-    <row r="361" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A361" s="5"/>
       <c r="B361" s="15" t="s">
         <v>48</v>
@@ -13248,7 +13294,7 @@
       <c r="K361" s="12"/>
       <c r="L361" s="12"/>
     </row>
-    <row r="362" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A362" s="5"/>
       <c r="B362" s="15" t="s">
         <v>48</v>
@@ -13270,7 +13316,7 @@
       <c r="K362" s="12"/>
       <c r="L362" s="12"/>
     </row>
-    <row r="363" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A363" s="5"/>
       <c r="B363" s="15" t="s">
         <v>48</v>
@@ -13292,7 +13338,7 @@
       <c r="K363" s="12"/>
       <c r="L363" s="12"/>
     </row>
-    <row r="364" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A364" s="5"/>
       <c r="B364" s="15" t="s">
         <v>48</v>
@@ -13314,7 +13360,7 @@
       <c r="K364" s="12"/>
       <c r="L364" s="12"/>
     </row>
-    <row r="365" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A365" s="5"/>
       <c r="B365" s="15" t="s">
         <v>48</v>
@@ -13336,7 +13382,7 @@
       <c r="K365" s="12"/>
       <c r="L365" s="12"/>
     </row>
-    <row r="366" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A366" s="5"/>
       <c r="B366" s="15" t="s">
         <v>48</v>
@@ -13358,7 +13404,7 @@
       <c r="K366" s="12"/>
       <c r="L366" s="12"/>
     </row>
-    <row r="367" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A367" s="5"/>
       <c r="B367" s="15" t="s">
         <v>48</v>
@@ -13380,7 +13426,7 @@
       <c r="K367" s="12"/>
       <c r="L367" s="12"/>
     </row>
-    <row r="368" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A368" s="5"/>
       <c r="B368" s="15" t="s">
         <v>48</v>
@@ -13402,7 +13448,7 @@
       <c r="K368" s="12"/>
       <c r="L368" s="12"/>
     </row>
-    <row r="369" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A369" s="5"/>
       <c r="B369" s="5" t="s">
         <v>21</v>
@@ -13434,7 +13480,7 @@
       </c>
       <c r="L369" s="12"/>
     </row>
-    <row r="370" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A370" s="5"/>
       <c r="B370" s="15" t="s">
         <v>48</v>
@@ -13456,7 +13502,7 @@
       <c r="K370" s="12"/>
       <c r="L370" s="12"/>
     </row>
-    <row r="371" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A371" s="5"/>
       <c r="B371" s="15" t="s">
         <v>48</v>
@@ -13478,7 +13524,7 @@
       <c r="K371" s="12"/>
       <c r="L371" s="12"/>
     </row>
-    <row r="372" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A372" s="5"/>
       <c r="B372" s="15" t="s">
         <v>48</v>
@@ -13500,7 +13546,7 @@
       <c r="K372" s="12"/>
       <c r="L372" s="12"/>
     </row>
-    <row r="373" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A373" s="5"/>
       <c r="B373" s="15" t="s">
         <v>48</v>
@@ -13522,7 +13568,7 @@
       <c r="K373" s="12"/>
       <c r="L373" s="12"/>
     </row>
-    <row r="374" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A374" s="5"/>
       <c r="B374" s="5" t="s">
         <v>21</v>
@@ -13554,7 +13600,7 @@
       </c>
       <c r="L374" s="12"/>
     </row>
-    <row r="375" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A375" s="5"/>
       <c r="B375" s="15" t="s">
         <v>48</v>
@@ -13576,7 +13622,7 @@
       <c r="K375" s="12"/>
       <c r="L375" s="12"/>
     </row>
-    <row r="376" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A376" s="5"/>
       <c r="B376" s="15" t="s">
         <v>48</v>
@@ -13598,7 +13644,7 @@
       <c r="K376" s="12"/>
       <c r="L376" s="12"/>
     </row>
-    <row r="377" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A377" s="5"/>
       <c r="B377" s="15" t="s">
         <v>48</v>
@@ -13620,7 +13666,7 @@
       <c r="K377" s="12"/>
       <c r="L377" s="12"/>
     </row>
-    <row r="378" spans="1:12" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A378" s="5"/>
       <c r="B378" s="5" t="s">
         <v>21</v>
@@ -13652,7 +13698,7 @@
       </c>
       <c r="L378" s="12"/>
     </row>
-    <row r="379" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A379" s="5"/>
       <c r="B379" s="15" t="s">
         <v>48</v>
@@ -13674,7 +13720,7 @@
       <c r="K379" s="12"/>
       <c r="L379" s="12"/>
     </row>
-    <row r="380" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A380" s="5"/>
       <c r="B380" s="15" t="s">
         <v>48</v>
@@ -13696,7 +13742,7 @@
       <c r="K380" s="12"/>
       <c r="L380" s="12"/>
     </row>
-    <row r="381" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A381" s="5"/>
       <c r="B381" s="15" t="s">
         <v>48</v>
@@ -13718,7 +13764,7 @@
       <c r="K381" s="12"/>
       <c r="L381" s="12"/>
     </row>
-    <row r="382" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A382" s="5"/>
       <c r="B382" s="15" t="s">
         <v>48</v>
@@ -13740,7 +13786,7 @@
       <c r="K382" s="12"/>
       <c r="L382" s="12"/>
     </row>
-    <row r="383" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A383" s="5"/>
       <c r="B383" s="15" t="s">
         <v>48</v>
@@ -13762,7 +13808,7 @@
       <c r="K383" s="12"/>
       <c r="L383" s="12"/>
     </row>
-    <row r="384" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A384" s="5"/>
       <c r="B384" s="15" t="s">
         <v>48</v>
@@ -13784,7 +13830,7 @@
       <c r="K384" s="12"/>
       <c r="L384" s="12"/>
     </row>
-    <row r="385" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A385" s="5"/>
       <c r="B385" s="15" t="s">
         <v>48</v>
@@ -13806,7 +13852,7 @@
       <c r="K385" s="12"/>
       <c r="L385" s="12"/>
     </row>
-    <row r="386" spans="1:12" customFormat="1" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A386" s="5"/>
       <c r="B386" s="15" t="s">
         <v>48</v>
@@ -13828,7 +13874,7 @@
       <c r="K386" s="12"/>
       <c r="L386" s="12"/>
     </row>
-    <row r="387" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A387" s="5"/>
       <c r="B387" s="15" t="s">
         <v>48</v>
@@ -13850,7 +13896,7 @@
       <c r="K387" s="12"/>
       <c r="L387" s="12"/>
     </row>
-    <row r="388" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A388" s="5"/>
       <c r="B388" s="15" t="s">
         <v>48</v>
@@ -13872,7 +13918,7 @@
       <c r="K388" s="12"/>
       <c r="L388" s="12"/>
     </row>
-    <row r="389" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A389" s="5"/>
       <c r="B389" s="5" t="s">
         <v>21</v>
@@ -13904,7 +13950,7 @@
       </c>
       <c r="L389" s="12"/>
     </row>
-    <row r="390" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="5"/>
       <c r="B390" s="5" t="s">
         <v>21</v>
@@ -13936,7 +13982,7 @@
       </c>
       <c r="L390" s="12"/>
     </row>
-    <row r="391" spans="1:12" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A391" s="5"/>
       <c r="B391" s="5" t="s">
         <v>21</v>
@@ -13968,7 +14014,7 @@
       </c>
       <c r="L391" s="12"/>
     </row>
-    <row r="392" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A392" s="5" t="s">
         <v>24</v>
       </c>
@@ -13988,7 +14034,7 @@
       <c r="K392" s="12"/>
       <c r="L392" s="12"/>
     </row>
-    <row r="393" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A393" s="5" t="s">
         <v>846</v>
       </c>
@@ -14008,7 +14054,7 @@
       <c r="K393" s="12"/>
       <c r="L393" s="12"/>
     </row>
-    <row r="394" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A394" s="5" t="s">
         <v>846</v>
       </c>
@@ -14028,7 +14074,7 @@
       <c r="K394" s="12"/>
       <c r="L394" s="12"/>
     </row>
-    <row r="395" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A395" s="5" t="s">
         <v>846</v>
       </c>
@@ -14048,7 +14094,7 @@
       <c r="K395" s="12"/>
       <c r="L395" s="12"/>
     </row>
-    <row r="396" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A396" s="5"/>
       <c r="B396" s="5" t="s">
         <v>932</v>
@@ -14066,7 +14112,7 @@
       <c r="K396" s="12"/>
       <c r="L396" s="12"/>
     </row>
-    <row r="397" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A397" s="5" t="s">
         <v>24</v>
       </c>
@@ -14086,7 +14132,7 @@
       <c r="K397" s="17"/>
       <c r="L397" s="17"/>
     </row>
-    <row r="398" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A398" s="5"/>
       <c r="B398" s="5" t="s">
         <v>932</v>
@@ -14104,7 +14150,7 @@
       <c r="K398" s="12"/>
       <c r="L398" s="12"/>
     </row>
-    <row r="399" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A399" s="5"/>
       <c r="B399" s="5" t="s">
         <v>932</v>
@@ -14122,7 +14168,7 @@
       <c r="K399" s="12"/>
       <c r="L399" s="12"/>
     </row>
-    <row r="400" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A400" s="5" t="s">
         <v>24</v>
       </c>
@@ -14142,7 +14188,7 @@
       <c r="K400" s="12"/>
       <c r="L400" s="12"/>
     </row>
-    <row r="401" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A401" s="5"/>
       <c r="B401" s="5" t="s">
         <v>932</v>
@@ -14160,7 +14206,7 @@
       <c r="K401" s="12"/>
       <c r="L401" s="12"/>
     </row>
-    <row r="402" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A402" s="5" t="s">
         <v>846</v>
       </c>
@@ -14180,7 +14226,7 @@
       <c r="K402" s="12"/>
       <c r="L402" s="12"/>
     </row>
-    <row r="403" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A403" s="5" t="s">
         <v>846</v>
       </c>
@@ -14200,7 +14246,7 @@
       <c r="K403" s="12"/>
       <c r="L403" s="12"/>
     </row>
-    <row r="404" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A404" s="5" t="s">
         <v>24</v>
       </c>
@@ -14220,7 +14266,7 @@
       <c r="K404" s="12"/>
       <c r="L404" s="12"/>
     </row>
-    <row r="405" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A405" s="5" t="s">
         <v>846</v>
       </c>
@@ -14240,7 +14286,7 @@
       <c r="K405" s="17"/>
       <c r="L405" s="17"/>
     </row>
-    <row r="406" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A406" s="5" t="s">
         <v>24</v>
       </c>
@@ -14260,7 +14306,7 @@
       <c r="K406" s="12"/>
       <c r="L406" s="12"/>
     </row>
-    <row r="407" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A407" s="5" t="s">
         <v>24</v>
       </c>
@@ -14280,7 +14326,7 @@
       <c r="K407" s="12"/>
       <c r="L407" s="12"/>
     </row>
-    <row r="408" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A408" s="5" t="s">
         <v>24</v>
       </c>
@@ -14300,7 +14346,7 @@
       <c r="K408" s="12"/>
       <c r="L408" s="12"/>
     </row>
-    <row r="409" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A409" s="5" t="s">
         <v>24</v>
       </c>
@@ -14320,7 +14366,7 @@
       <c r="K409" s="12"/>
       <c r="L409" s="12"/>
     </row>
-    <row r="410" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A410" s="5" t="s">
         <v>24</v>
       </c>
@@ -14340,67 +14386,71 @@
       <c r="K410" s="12"/>
       <c r="L410" s="12"/>
     </row>
-    <row r="411" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A411" s="5" t="s">
         <v>846</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C411" s="29" t="s">
-        <v>951</v>
-      </c>
-      <c r="D411" s="29" t="s">
-        <v>952</v>
-      </c>
-      <c r="E411" s="56" t="s">
+      <c r="C411" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D411" s="26" t="s">
+        <v>841</v>
+      </c>
+      <c r="E411" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F411" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G411" s="42"/>
+      <c r="F411" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G411" s="5"/>
       <c r="H411" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I411" s="36" t="s">
-        <v>856</v>
-      </c>
-      <c r="J411" s="42"/>
-      <c r="K411" s="42"/>
-      <c r="L411" s="42"/>
-    </row>
-    <row r="412" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="I411" s="36"/>
+      <c r="J411" s="5"/>
+      <c r="K411" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="L411" s="5" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A412" s="5" t="s">
         <v>846</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C412" s="29" t="s">
-        <v>953</v>
-      </c>
-      <c r="D412" s="29" t="s">
-        <v>954</v>
-      </c>
-      <c r="E412" s="56" t="s">
+      <c r="C412" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D412" s="26" t="s">
+        <v>845</v>
+      </c>
+      <c r="E412" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F412" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G412" s="42"/>
+      <c r="F412" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G412" s="5"/>
       <c r="H412" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I412" s="36" t="s">
-        <v>856</v>
-      </c>
-      <c r="J412" s="42"/>
-      <c r="K412" s="42"/>
-      <c r="L412" s="42"/>
-    </row>
-    <row r="413" spans="1:12" s="43" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+        <v>846</v>
+      </c>
+      <c r="J412" s="5"/>
+      <c r="K412" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="L412" s="5"/>
+    </row>
+    <row r="413" spans="1:12" s="43" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A413" s="5" t="s">
         <v>846</v>
       </c>
@@ -14408,29 +14458,31 @@
         <v>26</v>
       </c>
       <c r="C413" s="29" t="s">
-        <v>955</v>
-      </c>
-      <c r="D413" s="29" t="s">
-        <v>956</v>
-      </c>
-      <c r="E413" s="56" t="s">
+        <v>851</v>
+      </c>
+      <c r="D413" s="30" t="s">
+        <v>852</v>
+      </c>
+      <c r="E413" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F413" s="42" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G413" s="42"/>
       <c r="H413" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I413" s="36" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="J413" s="42"/>
-      <c r="K413" s="42"/>
+      <c r="K413" s="5" t="s">
+        <v>610</v>
+      </c>
       <c r="L413" s="42"/>
     </row>
-    <row r="414" spans="1:12" s="43" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" s="43" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A414" s="5" t="s">
         <v>846</v>
       </c>
@@ -14438,12 +14490,12 @@
         <v>26</v>
       </c>
       <c r="C414" s="29" t="s">
-        <v>957</v>
+        <v>854</v>
       </c>
       <c r="D414" s="29" t="s">
-        <v>958</v>
-      </c>
-      <c r="E414" s="56" t="s">
+        <v>855</v>
+      </c>
+      <c r="E414" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F414" s="42" t="s">
@@ -14460,7 +14512,7 @@
       <c r="K414" s="42"/>
       <c r="L414" s="42"/>
     </row>
-    <row r="415" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A415" s="5" t="s">
         <v>24</v>
       </c>
@@ -14480,7 +14532,7 @@
       <c r="K415" s="17"/>
       <c r="L415" s="17"/>
     </row>
-    <row r="416" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A416" s="5" t="s">
         <v>24</v>
       </c>
@@ -14500,7 +14552,7 @@
       <c r="K416" s="17"/>
       <c r="L416" s="17"/>
     </row>
-    <row r="417" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A417" s="5" t="s">
         <v>24</v>
       </c>
@@ -14520,7 +14572,7 @@
       <c r="K417" s="17"/>
       <c r="L417" s="17"/>
     </row>
-    <row r="418" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A418" s="5" t="s">
         <v>24</v>
       </c>
@@ -14540,7 +14592,7 @@
       <c r="K418" s="17"/>
       <c r="L418" s="17"/>
     </row>
-    <row r="419" spans="1:12" s="3" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" s="3" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A419" s="5" t="s">
         <v>24</v>
       </c>
@@ -14560,7 +14612,7 @@
       <c r="K419" s="17"/>
       <c r="L419" s="17"/>
     </row>
-    <row r="420" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A420" s="5" t="s">
         <v>24</v>
       </c>
@@ -14580,7 +14632,7 @@
       <c r="K420" s="12"/>
       <c r="L420" s="12"/>
     </row>
-    <row r="421" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A421" s="5" t="s">
         <v>24</v>
       </c>
@@ -14600,7 +14652,7 @@
       <c r="K421" s="12"/>
       <c r="L421" s="12"/>
     </row>
-    <row r="422" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A422" s="5" t="s">
         <v>24</v>
       </c>
@@ -14620,7 +14672,7 @@
       <c r="K422" s="12"/>
       <c r="L422" s="12"/>
     </row>
-    <row r="423" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A423" s="5" t="s">
         <v>24</v>
       </c>
@@ -14640,7 +14692,7 @@
       <c r="K423" s="12"/>
       <c r="L423" s="12"/>
     </row>
-    <row r="424" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A424" s="5" t="s">
         <v>24</v>
       </c>
@@ -14660,7 +14712,7 @@
       <c r="K424" s="12"/>
       <c r="L424" s="12"/>
     </row>
-    <row r="425" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A425" s="5" t="s">
         <v>24</v>
       </c>
@@ -14680,7 +14732,7 @@
       <c r="K425" s="12"/>
       <c r="L425" s="12"/>
     </row>
-    <row r="426" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A426" s="5" t="s">
         <v>846</v>
       </c>
@@ -14700,7 +14752,7 @@
       <c r="K426" s="12"/>
       <c r="L426" s="12"/>
     </row>
-    <row r="427" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A427" s="5" t="s">
         <v>24</v>
       </c>
@@ -14720,7 +14772,7 @@
       <c r="K427" s="12"/>
       <c r="L427" s="12"/>
     </row>
-    <row r="428" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A428" s="5" t="s">
         <v>24</v>
       </c>
@@ -14740,7 +14792,7 @@
       <c r="K428" s="12"/>
       <c r="L428" s="12"/>
     </row>
-    <row r="429" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A429" s="5" t="s">
         <v>24</v>
       </c>
@@ -14760,7 +14812,7 @@
       <c r="K429" s="12"/>
       <c r="L429" s="12"/>
     </row>
-    <row r="430" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A430" s="5" t="s">
         <v>24</v>
       </c>
@@ -14780,7 +14832,7 @@
       <c r="K430" s="12"/>
       <c r="L430" s="12"/>
     </row>
-    <row r="431" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A431" s="5" t="s">
         <v>24</v>
       </c>
@@ -14800,7 +14852,7 @@
       <c r="K431" s="12"/>
       <c r="L431" s="12"/>
     </row>
-    <row r="432" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A432" s="5" t="s">
         <v>24</v>
       </c>
@@ -14820,7 +14872,7 @@
       <c r="K432" s="12"/>
       <c r="L432" s="12"/>
     </row>
-    <row r="433" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A433" s="5" t="s">
         <v>24</v>
       </c>
@@ -14840,7 +14892,7 @@
       <c r="K433" s="12"/>
       <c r="L433" s="12"/>
     </row>
-    <row r="434" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A434" s="5" t="s">
         <v>24</v>
       </c>
@@ -14860,7 +14912,7 @@
       <c r="K434" s="12"/>
       <c r="L434" s="12"/>
     </row>
-    <row r="435" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A435" s="5" t="s">
         <v>24</v>
       </c>
@@ -14880,7 +14932,7 @@
       <c r="K435" s="12"/>
       <c r="L435" s="12"/>
     </row>
-    <row r="436" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A436" s="5" t="s">
         <v>24</v>
       </c>
@@ -14900,7 +14952,7 @@
       <c r="K436" s="12"/>
       <c r="L436" s="12"/>
     </row>
-    <row r="437" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A437" s="5" t="s">
         <v>846</v>
       </c>
@@ -14920,7 +14972,7 @@
       <c r="K437" s="12"/>
       <c r="L437" s="12"/>
     </row>
-    <row r="438" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A438" s="5" t="s">
         <v>846</v>
       </c>
@@ -14940,7 +14992,7 @@
       <c r="K438" s="12"/>
       <c r="L438" s="12"/>
     </row>
-    <row r="439" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A439" s="5" t="s">
         <v>24</v>
       </c>
@@ -14960,7 +15012,7 @@
       <c r="K439" s="12"/>
       <c r="L439" s="12"/>
     </row>
-    <row r="440" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A440" s="5" t="s">
         <v>24</v>
       </c>
@@ -14980,7 +15032,7 @@
       <c r="K440" s="12"/>
       <c r="L440" s="12"/>
     </row>
-    <row r="441" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A441" s="5" t="s">
         <v>24</v>
       </c>
@@ -15000,7 +15052,7 @@
       <c r="K441" s="12"/>
       <c r="L441" s="12"/>
     </row>
-    <row r="442" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A442" s="5" t="s">
         <v>24</v>
       </c>
@@ -15020,7 +15072,7 @@
       <c r="K442" s="12"/>
       <c r="L442" s="12"/>
     </row>
-    <row r="443" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A443" s="5" t="s">
         <v>24</v>
       </c>
@@ -15040,7 +15092,7 @@
       <c r="K443" s="12"/>
       <c r="L443" s="12"/>
     </row>
-    <row r="444" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A444" s="5" t="s">
         <v>24</v>
       </c>
@@ -15060,7 +15112,7 @@
       <c r="K444" s="12"/>
       <c r="L444" s="12"/>
     </row>
-    <row r="445" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A445" s="5" t="s">
         <v>846</v>
       </c>
@@ -15080,7 +15132,7 @@
       <c r="K445" s="12"/>
       <c r="L445" s="12"/>
     </row>
-    <row r="446" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A446" s="5" t="s">
         <v>24</v>
       </c>
@@ -15100,7 +15152,7 @@
       <c r="K446" s="12"/>
       <c r="L446" s="12"/>
     </row>
-    <row r="447" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A447" s="5" t="s">
         <v>24</v>
       </c>
@@ -15120,7 +15172,7 @@
       <c r="K447" s="12"/>
       <c r="L447" s="12"/>
     </row>
-    <row r="448" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A448" s="5" t="s">
         <v>24</v>
       </c>
@@ -15140,7 +15192,7 @@
       <c r="K448" s="12"/>
       <c r="L448" s="12"/>
     </row>
-    <row r="449" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A449" s="5" t="s">
         <v>24</v>
       </c>
@@ -15160,7 +15212,7 @@
       <c r="K449" s="12"/>
       <c r="L449" s="12"/>
     </row>
-    <row r="450" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A450" s="5" t="s">
         <v>24</v>
       </c>
@@ -15180,7 +15232,7 @@
       <c r="K450" s="12"/>
       <c r="L450" s="12"/>
     </row>
-    <row r="451" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A451" s="5" t="s">
         <v>846</v>
       </c>
@@ -15200,7 +15252,7 @@
       <c r="K451" s="12"/>
       <c r="L451" s="12"/>
     </row>
-    <row r="452" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A452" s="5" t="s">
         <v>846</v>
       </c>
@@ -15220,7 +15272,7 @@
       <c r="K452" s="12"/>
       <c r="L452" s="12"/>
     </row>
-    <row r="453" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A453" s="5" t="s">
         <v>846</v>
       </c>
@@ -15240,7 +15292,7 @@
       <c r="K453" s="12"/>
       <c r="L453" s="12"/>
     </row>
-    <row r="454" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A454" s="5" t="s">
         <v>24</v>
       </c>
@@ -15260,7 +15312,7 @@
       <c r="K454" s="12"/>
       <c r="L454" s="12"/>
     </row>
-    <row r="455" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A455" s="5" t="s">
         <v>24</v>
       </c>
@@ -15280,7 +15332,7 @@
       <c r="K455" s="12"/>
       <c r="L455" s="12"/>
     </row>
-    <row r="456" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A456" s="5" t="s">
         <v>24</v>
       </c>
@@ -15300,7 +15352,7 @@
       <c r="K456" s="12"/>
       <c r="L456" s="12"/>
     </row>
-    <row r="457" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A457" s="5" t="s">
         <v>24</v>
       </c>
@@ -15320,7 +15372,7 @@
       <c r="K457" s="12"/>
       <c r="L457" s="12"/>
     </row>
-    <row r="458" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A458" s="5" t="s">
         <v>24</v>
       </c>
@@ -15340,7 +15392,7 @@
       <c r="K458" s="12"/>
       <c r="L458" s="12"/>
     </row>
-    <row r="459" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A459" s="5" t="s">
         <v>24</v>
       </c>
@@ -15360,7 +15412,7 @@
       <c r="K459" s="12"/>
       <c r="L459" s="12"/>
     </row>
-    <row r="460" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A460" s="5" t="s">
         <v>24</v>
       </c>
@@ -15380,7 +15432,7 @@
       <c r="K460" s="12"/>
       <c r="L460" s="12"/>
     </row>
-    <row r="461" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A461" s="5" t="s">
         <v>24</v>
       </c>
@@ -15400,7 +15452,7 @@
       <c r="K461" s="12"/>
       <c r="L461" s="12"/>
     </row>
-    <row r="462" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A462" s="5" t="s">
         <v>24</v>
       </c>
@@ -15420,7 +15472,7 @@
       <c r="K462" s="12"/>
       <c r="L462" s="12"/>
     </row>
-    <row r="463" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A463" s="5" t="s">
         <v>24</v>
       </c>
@@ -15440,7 +15492,7 @@
       <c r="K463" s="12"/>
       <c r="L463" s="12"/>
     </row>
-    <row r="464" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A464" s="5" t="s">
         <v>24</v>
       </c>
@@ -15460,7 +15512,7 @@
       <c r="K464" s="12"/>
       <c r="L464" s="12"/>
     </row>
-    <row r="465" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A465" s="5" t="s">
         <v>24</v>
       </c>
@@ -15480,7 +15532,7 @@
       <c r="K465" s="12"/>
       <c r="L465" s="12"/>
     </row>
-    <row r="466" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A466" s="5" t="s">
         <v>24</v>
       </c>
@@ -15500,7 +15552,7 @@
       <c r="K466" s="12"/>
       <c r="L466" s="12"/>
     </row>
-    <row r="467" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A467" s="5" t="s">
         <v>24</v>
       </c>
@@ -15520,7 +15572,7 @@
       <c r="K467" s="12"/>
       <c r="L467" s="12"/>
     </row>
-    <row r="468" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A468" s="5" t="s">
         <v>24</v>
       </c>
@@ -15540,7 +15592,7 @@
       <c r="K468" s="12"/>
       <c r="L468" s="12"/>
     </row>
-    <row r="469" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A469" s="5" t="s">
         <v>24</v>
       </c>
@@ -15560,7 +15612,7 @@
       <c r="K469" s="12"/>
       <c r="L469" s="12"/>
     </row>
-    <row r="470" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A470" s="5" t="s">
         <v>24</v>
       </c>
@@ -15580,7 +15632,7 @@
       <c r="K470" s="12"/>
       <c r="L470" s="12"/>
     </row>
-    <row r="471" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A471" s="5" t="s">
         <v>24</v>
       </c>
@@ -15600,7 +15652,7 @@
       <c r="K471" s="12"/>
       <c r="L471" s="12"/>
     </row>
-    <row r="472" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A472" s="5" t="s">
         <v>24</v>
       </c>
@@ -15620,7 +15672,7 @@
       <c r="K472" s="12"/>
       <c r="L472" s="12"/>
     </row>
-    <row r="473" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A473" s="5" t="s">
         <v>24</v>
       </c>
@@ -15640,7 +15692,7 @@
       <c r="K473" s="12"/>
       <c r="L473" s="12"/>
     </row>
-    <row r="474" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A474" s="5" t="s">
         <v>24</v>
       </c>
@@ -15660,7 +15712,7 @@
       <c r="K474" s="12"/>
       <c r="L474" s="12"/>
     </row>
-    <row r="475" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A475" s="5" t="s">
         <v>24</v>
       </c>
@@ -15680,7 +15732,7 @@
       <c r="K475" s="12"/>
       <c r="L475" s="12"/>
     </row>
-    <row r="476" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A476" s="5" t="s">
         <v>24</v>
       </c>
@@ -15700,7 +15752,7 @@
       <c r="K476" s="12"/>
       <c r="L476" s="12"/>
     </row>
-    <row r="477" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A477" s="5" t="s">
         <v>24</v>
       </c>
@@ -15720,7 +15772,7 @@
       <c r="K477" s="12"/>
       <c r="L477" s="12"/>
     </row>
-    <row r="478" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A478" s="5" t="s">
         <v>24</v>
       </c>
@@ -15740,7 +15792,7 @@
       <c r="K478" s="12"/>
       <c r="L478" s="12"/>
     </row>
-    <row r="479" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A479" s="5" t="s">
         <v>846</v>
       </c>
@@ -15760,7 +15812,7 @@
       <c r="K479" s="12"/>
       <c r="L479" s="12"/>
     </row>
-    <row r="480" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A480" s="5" t="s">
         <v>846</v>
       </c>
@@ -15780,7 +15832,7 @@
       <c r="K480" s="12"/>
       <c r="L480" s="12"/>
     </row>
-    <row r="481" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A481" s="5" t="s">
         <v>846</v>
       </c>
@@ -15800,7 +15852,7 @@
       <c r="K481" s="12"/>
       <c r="L481" s="12"/>
     </row>
-    <row r="482" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A482" s="5" t="s">
         <v>846</v>
       </c>
@@ -15820,7 +15872,7 @@
       <c r="K482" s="12"/>
       <c r="L482" s="12"/>
     </row>
-    <row r="483" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A483" s="5" t="s">
         <v>846</v>
       </c>
@@ -15840,7 +15892,7 @@
       <c r="K483" s="12"/>
       <c r="L483" s="12"/>
     </row>
-    <row r="484" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A484" s="5" t="s">
         <v>846</v>
       </c>
@@ -15860,7 +15912,7 @@
       <c r="K484" s="12"/>
       <c r="L484" s="12"/>
     </row>
-    <row r="485" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A485" s="5" t="s">
         <v>24</v>
       </c>
@@ -15880,7 +15932,7 @@
       <c r="K485" s="12"/>
       <c r="L485" s="12"/>
     </row>
-    <row r="486" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A486" s="5" t="s">
         <v>24</v>
       </c>
@@ -15900,7 +15952,7 @@
       <c r="K486" s="12"/>
       <c r="L486" s="12"/>
     </row>
-    <row r="487" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A487" s="5" t="s">
         <v>24</v>
       </c>
@@ -15920,7 +15972,7 @@
       <c r="K487" s="12"/>
       <c r="L487" s="12"/>
     </row>
-    <row r="488" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A488" s="5" t="s">
         <v>24</v>
       </c>
@@ -15940,7 +15992,7 @@
       <c r="K488" s="12"/>
       <c r="L488" s="12"/>
     </row>
-    <row r="489" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A489" s="5" t="s">
         <v>24</v>
       </c>
@@ -15960,7 +16012,7 @@
       <c r="K489" s="12"/>
       <c r="L489" s="12"/>
     </row>
-    <row r="490" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A490" s="5" t="s">
         <v>24</v>
       </c>
@@ -15980,7 +16032,7 @@
       <c r="K490" s="12"/>
       <c r="L490" s="12"/>
     </row>
-    <row r="491" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A491" s="5" t="s">
         <v>24</v>
       </c>
@@ -16000,7 +16052,7 @@
       <c r="K491" s="12"/>
       <c r="L491" s="12"/>
     </row>
-    <row r="492" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A492" s="5" t="s">
         <v>24</v>
       </c>
@@ -16020,7 +16072,7 @@
       <c r="K492" s="12"/>
       <c r="L492" s="12"/>
     </row>
-    <row r="493" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A493" s="5" t="s">
         <v>24</v>
       </c>
@@ -16040,7 +16092,7 @@
       <c r="K493" s="12"/>
       <c r="L493" s="12"/>
     </row>
-    <row r="494" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A494" s="5" t="s">
         <v>24</v>
       </c>
@@ -16060,7 +16112,7 @@
       <c r="K494" s="12"/>
       <c r="L494" s="12"/>
     </row>
-    <row r="495" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A495" s="5" t="s">
         <v>24</v>
       </c>
@@ -16080,7 +16132,7 @@
       <c r="K495" s="12"/>
       <c r="L495" s="12"/>
     </row>
-    <row r="496" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A496" s="5" t="s">
         <v>24</v>
       </c>
@@ -16100,7 +16152,7 @@
       <c r="K496" s="12"/>
       <c r="L496" s="12"/>
     </row>
-    <row r="497" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A497" s="5" t="s">
         <v>24</v>
       </c>
@@ -16120,7 +16172,7 @@
       <c r="K497" s="12"/>
       <c r="L497" s="12"/>
     </row>
-    <row r="498" spans="1:12" customFormat="1" ht="15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A498" s="5" t="s">
         <v>24</v>
       </c>
@@ -16140,18 +16192,18 @@
       <c r="K498" s="12"/>
       <c r="L498" s="12"/>
     </row>
-    <row r="499" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A499" s="42"/>
       <c r="B499" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C499" s="29" t="s">
-        <v>1043</v>
+        <v>861</v>
       </c>
       <c r="D499" s="29" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E499" s="56" t="s">
+        <v>862</v>
+      </c>
+      <c r="E499" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F499" s="42" t="s">
@@ -16168,18 +16220,18 @@
       <c r="K499" s="42"/>
       <c r="L499" s="42"/>
     </row>
-    <row r="500" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A500" s="42"/>
       <c r="B500" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C500" s="29" t="s">
-        <v>1045</v>
+        <v>863</v>
       </c>
       <c r="D500" s="29" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E500" s="56" t="s">
+        <v>864</v>
+      </c>
+      <c r="E500" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F500" s="42" t="s">
@@ -16196,18 +16248,18 @@
       <c r="K500" s="42"/>
       <c r="L500" s="42"/>
     </row>
-    <row r="501" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A501" s="42"/>
       <c r="B501" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C501" s="29" t="s">
-        <v>1047</v>
+        <v>951</v>
       </c>
       <c r="D501" s="29" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E501" s="56" t="s">
+        <v>952</v>
+      </c>
+      <c r="E501" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F501" s="42" t="s">
@@ -16224,213 +16276,201 @@
       <c r="K501" s="42"/>
       <c r="L501" s="42"/>
     </row>
-    <row r="502" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A502" s="42"/>
       <c r="B502" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C502" s="8" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D502" s="25" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E502" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="F502" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="G502" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="C502" s="29" t="s">
+        <v>953</v>
+      </c>
+      <c r="D502" s="29" t="s">
+        <v>954</v>
+      </c>
+      <c r="E502" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="F502" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G502" s="42"/>
       <c r="H502" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I502" s="37"/>
-      <c r="J502" s="38">
-        <v>127</v>
-      </c>
-      <c r="K502" s="6"/>
-      <c r="L502" s="39"/>
-    </row>
-    <row r="503" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I502" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J502" s="42"/>
+      <c r="K502" s="42"/>
+      <c r="L502" s="42"/>
+    </row>
+    <row r="503" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A503" s="42"/>
       <c r="B503" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C503" s="8" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D503" s="28" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E503" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C503" s="29" t="s">
+        <v>955</v>
+      </c>
+      <c r="D503" s="29" t="s">
+        <v>956</v>
+      </c>
+      <c r="E503" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F503" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G503" s="6"/>
+      <c r="F503" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G503" s="42"/>
       <c r="H503" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I503" s="37" t="s">
-        <v>1053</v>
-      </c>
-      <c r="J503" s="38">
-        <v>66</v>
-      </c>
-      <c r="K503" s="6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="L503" s="5"/>
-    </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I503" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J503" s="42"/>
+      <c r="K503" s="42"/>
+      <c r="L503" s="42"/>
+    </row>
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="42"/>
       <c r="B504" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C504" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D504" s="24" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E504" s="56" t="s">
+      <c r="C504" s="29" t="s">
+        <v>957</v>
+      </c>
+      <c r="D504" s="29" t="s">
+        <v>958</v>
+      </c>
+      <c r="E504" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F504" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G504" s="5"/>
+      <c r="F504" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G504" s="42"/>
       <c r="H504" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I504" s="36"/>
-      <c r="J504" s="5"/>
-      <c r="K504" s="5"/>
-      <c r="L504" s="5"/>
-    </row>
-    <row r="505" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I504" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J504" s="42"/>
+      <c r="K504" s="42"/>
+      <c r="L504" s="42"/>
+    </row>
+    <row r="505" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A505" s="42"/>
       <c r="B505" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C505" s="8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D505" s="25" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E505" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C505" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D505" s="29" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E505" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F505" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G505" s="6"/>
+      <c r="F505" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G505" s="42"/>
       <c r="H505" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I505" s="37"/>
-      <c r="J505" s="38">
-        <v>159</v>
-      </c>
-      <c r="K505" s="6" t="s">
-        <v>1059</v>
-      </c>
-      <c r="L505" s="6"/>
-    </row>
-    <row r="506" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="I505" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J505" s="42"/>
+      <c r="K505" s="42"/>
+      <c r="L505" s="42"/>
+    </row>
+    <row r="506" spans="1:12" ht="69" x14ac:dyDescent="0.3">
       <c r="A506" s="42"/>
       <c r="B506" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C506" s="8" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D506" s="25" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E506" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C506" s="29" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D506" s="29" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E506" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F506" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G506" s="6"/>
+      <c r="F506" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G506" s="42"/>
       <c r="H506" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I506" s="37"/>
-      <c r="J506" s="38">
-        <v>159</v>
-      </c>
-      <c r="K506" s="6" t="s">
-        <v>1062</v>
-      </c>
-      <c r="L506" s="6"/>
-    </row>
-    <row r="507" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="I506" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J506" s="42"/>
+      <c r="K506" s="42"/>
+      <c r="L506" s="42"/>
+    </row>
+    <row r="507" spans="1:12" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A507" s="42"/>
       <c r="B507" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C507" s="8" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D507" s="25" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E507" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C507" s="29" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D507" s="29" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E507" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F507" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G507" s="6"/>
+      <c r="F507" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="G507" s="42"/>
       <c r="H507" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I507" s="37"/>
-      <c r="J507" s="38">
-        <v>159</v>
-      </c>
-      <c r="K507" s="6" t="s">
-        <v>1059</v>
-      </c>
-      <c r="L507" s="6"/>
-    </row>
-    <row r="508" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="I507" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="J507" s="42"/>
+      <c r="K507" s="42"/>
+      <c r="L507" s="42"/>
+    </row>
+    <row r="508" spans="1:12" ht="69" x14ac:dyDescent="0.3">
       <c r="A508" s="42"/>
       <c r="B508" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C508" s="8" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D508" s="25" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E508" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C508" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D508" s="24" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E508" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="F508" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G508" s="6"/>
+      <c r="F508" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G508" s="5"/>
       <c r="H508" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I508" s="37"/>
-      <c r="J508" s="38">
-        <v>159</v>
-      </c>
-      <c r="K508" s="6" t="s">
-        <v>1062</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I508" s="36"/>
+      <c r="J508" s="5"/>
+      <c r="K508" s="5"/>
       <c r="L508" s="5"/>
     </row>
-    <row r="509" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A509" s="42"/>
       <c r="B509" s="5" t="s">
         <v>26</v>
@@ -16441,7 +16481,7 @@
       <c r="D509" s="16" t="s">
         <v>1068</v>
       </c>
-      <c r="E509" s="56" t="s">
+      <c r="E509" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F509" s="6" t="s">
@@ -16458,7 +16498,7 @@
       </c>
       <c r="L509" s="5"/>
     </row>
-    <row r="510" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="69" x14ac:dyDescent="0.3">
       <c r="A510" s="42"/>
       <c r="B510" s="5" t="s">
         <v>26</v>
@@ -16469,7 +16509,7 @@
       <c r="D510" s="16" t="s">
         <v>1071</v>
       </c>
-      <c r="E510" s="56" t="s">
+      <c r="E510" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F510" s="6" t="s">
@@ -16488,7 +16528,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A511" s="42"/>
       <c r="B511" s="5" t="s">
         <v>26</v>
@@ -16497,7 +16537,7 @@
       <c r="D511" s="16" t="s">
         <v>1074</v>
       </c>
-      <c r="E511" s="56" t="s">
+      <c r="E511" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F511" s="6" t="s">
@@ -16514,7 +16554,7 @@
       </c>
       <c r="L511" s="5"/>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="45"/>
       <c r="B512" s="45" t="s">
         <v>26</v>
@@ -16538,7 +16578,7 @@
       <c r="K512" s="48"/>
       <c r="L512" s="48"/>
     </row>
-    <row r="513" spans="1:12" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A513" s="42"/>
       <c r="B513" s="5" t="s">
         <v>26</v>
@@ -16547,7 +16587,7 @@
       <c r="D513" s="16" t="s">
         <v>1077</v>
       </c>
-      <c r="E513" s="56" t="s">
+      <c r="E513" s="54" t="s">
         <v>15</v>
       </c>
       <c r="F513" s="6" t="s">
@@ -16557,7 +16597,7 @@
       <c r="H513" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I513" s="54" t="s">
+      <c r="I513" s="52" t="s">
         <v>1078</v>
       </c>
       <c r="J513" s="5"/>
@@ -16570,14 +16610,8 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:L513" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="DEET"/>
-        <filter val="Navigator/DEET"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L512">
-      <sortCondition ref="C1:C512"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L513">
+      <sortCondition descending="1" ref="B1:B513"/>
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
